--- a/GBDS APRIL FILES 2026/Guillermo DOS 2 - Neilven.xlsx
+++ b/GBDS APRIL FILES 2026/Guillermo DOS 2 - Neilven.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS MARCH FILES 2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS APRIL FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50C75C33-B3F2-4CAC-BD6A-27817E9292B9}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F32DF6E-5230-4A77-9557-6A59849E00C5}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="131">
   <si>
     <t>DEALER NAME:</t>
   </si>
@@ -446,9 +446,6 @@
   </si>
   <si>
     <t>SML500C</t>
-  </si>
-  <si>
-    <t>RETURN NO.</t>
   </si>
 </sst>
 </file>
@@ -646,7 +643,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="66">
+  <borders count="67">
     <border>
       <left/>
       <right/>
@@ -1467,9 +1464,28 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="medium">
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
         <color indexed="64"/>
       </top>
       <bottom style="thin">
@@ -1484,7 +1500,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="298">
+  <cellXfs count="299">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
@@ -2082,344 +2098,348 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="65" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="63" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="167" fontId="19" fillId="0" borderId="63" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="43" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="54" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="43" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="58" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="59" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="52" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="53" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="43" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="54" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="55" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="57" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="52" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="48" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="53" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="43" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="54" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="55" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="56" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="57" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="52" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="55" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="53" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="54" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="57" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="52" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="43" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="55" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="52" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="43" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="55" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="48" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="25" fillId="0" borderId="50" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="25" fillId="0" borderId="51" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="49" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="50" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="26" fillId="0" borderId="49" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="51" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="25" fillId="0" borderId="49" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="63" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="43" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="19" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="28" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="26" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="15" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="16" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="17" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="24" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="25" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="27" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="53" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="54" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="57" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="17" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="63" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="49" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="51" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="167" fontId="19" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="167" fontId="19" fillId="0" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="167" fontId="19" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="167" fontId="19" fillId="0" borderId="26" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="167" fontId="19" fillId="0" borderId="28" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="167" fontId="19" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="167" fontId="19" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="167" fontId="19" fillId="0" borderId="62" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="167" fontId="19" fillId="0" borderId="41" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="63" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="49" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="51" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="63" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="63" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="19" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="28" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="26" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="15" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="16" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="17" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="24" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="25" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="27" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="53" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="54" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="57" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="17" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="48" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="25" fillId="0" borderId="50" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="25" fillId="0" borderId="51" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="49" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="50" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="26" fillId="0" borderId="49" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="51" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="25" fillId="0" borderId="49" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="43" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="43" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="54" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="43" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="58" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="167" fontId="19" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="167" fontId="19" fillId="0" borderId="41" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="59" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="167" fontId="19" fillId="0" borderId="28" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="52" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="53" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="43" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="54" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="55" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="57" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="167" fontId="19" fillId="0" borderId="62" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="167" fontId="19" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="167" fontId="19" fillId="0" borderId="63" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="52" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="48" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="53" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="43" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="54" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="55" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="56" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="57" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="52" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="55" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="53" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="167" fontId="19" fillId="0" borderId="26" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="54" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="65" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="57" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="52" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="43" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="55" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="52" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="43" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="55" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="66" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -2965,35 +2985,35 @@
         <v>320</v>
       </c>
     </row>
-    <row r="2" spans="2:35" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:35" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="93" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="93"/>
       <c r="D2" s="93"/>
       <c r="E2" s="93"/>
-      <c r="F2" s="208" t="s">
+      <c r="F2" s="285" t="s">
         <v>85</v>
       </c>
-      <c r="G2" s="208"/>
-      <c r="H2" s="208"/>
-      <c r="I2" s="208"/>
-      <c r="J2" s="208"/>
-      <c r="K2" s="208"/>
-      <c r="L2" s="208"/>
-      <c r="M2" s="208"/>
-      <c r="N2" s="208"/>
-      <c r="O2" s="208"/>
-      <c r="P2" s="208"/>
-      <c r="Q2" s="208"/>
-      <c r="R2" s="208"/>
-      <c r="S2" s="208"/>
+      <c r="G2" s="285"/>
+      <c r="H2" s="285"/>
+      <c r="I2" s="285"/>
+      <c r="J2" s="285"/>
+      <c r="K2" s="285"/>
+      <c r="L2" s="285"/>
+      <c r="M2" s="285"/>
+      <c r="N2" s="285"/>
+      <c r="O2" s="285"/>
+      <c r="P2" s="285"/>
+      <c r="Q2" s="285"/>
+      <c r="R2" s="285"/>
+      <c r="S2" s="285"/>
       <c r="T2" s="94" t="s">
         <v>1</v>
       </c>
-      <c r="U2" s="215"/>
-      <c r="V2" s="215"/>
-      <c r="X2" s="209" t="s">
+      <c r="U2" s="298"/>
+      <c r="V2" s="297"/>
+      <c r="X2" s="238" t="s">
         <v>2</v>
       </c>
       <c r="AB2" s="92">
@@ -3028,12 +3048,10 @@
       <c r="Q3" s="193"/>
       <c r="R3" s="193"/>
       <c r="S3" s="193"/>
-      <c r="T3" s="94" t="s">
-        <v>131</v>
-      </c>
-      <c r="U3" s="194"/>
-      <c r="V3" s="194"/>
-      <c r="X3" s="210"/>
+      <c r="T3" s="94"/>
+      <c r="U3" s="298"/>
+      <c r="V3" s="297"/>
+      <c r="X3" s="239"/>
       <c r="AB3" s="92"/>
       <c r="AE3" s="92"/>
     </row>
@@ -3042,7 +3060,8 @@
       <c r="C4" s="93"/>
       <c r="D4" s="93"/>
       <c r="E4" s="93"/>
-      <c r="X4" s="210"/>
+      <c r="U4" s="186"/>
+      <c r="X4" s="239"/>
       <c r="AB4" s="92">
         <v>5.76</v>
       </c>
@@ -3063,21 +3082,21 @@
       <c r="C5" s="93"/>
       <c r="D5" s="93"/>
       <c r="E5" s="93"/>
-      <c r="F5" s="212"/>
-      <c r="G5" s="212"/>
-      <c r="H5" s="212"/>
-      <c r="I5" s="212"/>
-      <c r="J5" s="212"/>
-      <c r="K5" s="212"/>
-      <c r="L5" s="212"/>
-      <c r="M5" s="212"/>
+      <c r="F5" s="286"/>
+      <c r="G5" s="286"/>
+      <c r="H5" s="286"/>
+      <c r="I5" s="286"/>
+      <c r="J5" s="286"/>
+      <c r="K5" s="286"/>
+      <c r="L5" s="286"/>
+      <c r="M5" s="286"/>
       <c r="S5" s="91" t="s">
         <v>4</v>
       </c>
-      <c r="T5" s="213"/>
-      <c r="U5" s="213"/>
+      <c r="T5" s="287"/>
+      <c r="U5" s="287"/>
       <c r="V5" s="183"/>
-      <c r="X5" s="211"/>
+      <c r="X5" s="240"/>
       <c r="AB5" s="92">
         <v>5.07</v>
       </c>
@@ -3119,25 +3138,25 @@
       <c r="B7" s="91" t="s">
         <v>5</v>
       </c>
-      <c r="F7" s="214"/>
-      <c r="G7" s="214"/>
-      <c r="H7" s="214"/>
-      <c r="I7" s="214"/>
-      <c r="J7" s="214"/>
-      <c r="K7" s="214"/>
-      <c r="L7" s="214"/>
-      <c r="M7" s="214"/>
+      <c r="F7" s="288"/>
+      <c r="G7" s="288"/>
+      <c r="H7" s="288"/>
+      <c r="I7" s="288"/>
+      <c r="J7" s="288"/>
+      <c r="K7" s="288"/>
+      <c r="L7" s="288"/>
+      <c r="M7" s="288"/>
       <c r="S7" s="97" t="s">
         <v>6</v>
       </c>
       <c r="T7" s="163" t="s">
         <v>7</v>
       </c>
-      <c r="U7" s="205" t="s">
+      <c r="U7" s="280" t="s">
         <v>8</v>
       </c>
-      <c r="V7" s="205"/>
-      <c r="X7" s="209" t="s">
+      <c r="V7" s="280"/>
+      <c r="X7" s="238" t="s">
         <v>9</v>
       </c>
       <c r="AB7" s="92">
@@ -3160,14 +3179,14 @@
       <c r="C8" s="98"/>
       <c r="D8" s="98"/>
       <c r="E8" s="98"/>
-      <c r="F8" s="214"/>
-      <c r="G8" s="214"/>
-      <c r="H8" s="214"/>
-      <c r="I8" s="214"/>
-      <c r="J8" s="214"/>
-      <c r="K8" s="214"/>
-      <c r="L8" s="214"/>
-      <c r="M8" s="214"/>
+      <c r="F8" s="288"/>
+      <c r="G8" s="288"/>
+      <c r="H8" s="288"/>
+      <c r="I8" s="288"/>
+      <c r="J8" s="288"/>
+      <c r="K8" s="288"/>
+      <c r="L8" s="288"/>
+      <c r="M8" s="288"/>
       <c r="N8" s="99"/>
       <c r="O8" s="99"/>
       <c r="P8" s="99"/>
@@ -3176,9 +3195,9 @@
       <c r="T8" s="163" t="s">
         <v>11</v>
       </c>
-      <c r="U8" s="206"/>
-      <c r="V8" s="207"/>
-      <c r="X8" s="211"/>
+      <c r="U8" s="281"/>
+      <c r="V8" s="282"/>
+      <c r="X8" s="240"/>
       <c r="AB8" s="92">
         <v>5.25</v>
       </c>
@@ -3212,127 +3231,127 @@
       <c r="V9" s="95"/>
     </row>
     <row r="10" spans="2:35" s="100" customFormat="1" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="217" t="s">
+      <c r="B10" s="248" t="s">
         <v>12</v>
       </c>
-      <c r="C10" s="220" t="s">
+      <c r="C10" s="251" t="s">
         <v>13</v>
       </c>
-      <c r="D10" s="220" t="s">
+      <c r="D10" s="251" t="s">
         <v>14</v>
       </c>
-      <c r="E10" s="220" t="s">
+      <c r="E10" s="251" t="s">
         <v>15</v>
       </c>
-      <c r="F10" s="223" t="s">
+      <c r="F10" s="254" t="s">
         <v>16</v>
       </c>
-      <c r="G10" s="224"/>
-      <c r="H10" s="224"/>
-      <c r="I10" s="224"/>
-      <c r="J10" s="224"/>
-      <c r="K10" s="224"/>
-      <c r="L10" s="224"/>
-      <c r="M10" s="224"/>
-      <c r="N10" s="224"/>
-      <c r="O10" s="224"/>
-      <c r="P10" s="224"/>
-      <c r="Q10" s="225"/>
-      <c r="S10" s="216" t="s">
+      <c r="G10" s="255"/>
+      <c r="H10" s="255"/>
+      <c r="I10" s="255"/>
+      <c r="J10" s="255"/>
+      <c r="K10" s="255"/>
+      <c r="L10" s="255"/>
+      <c r="M10" s="255"/>
+      <c r="N10" s="255"/>
+      <c r="O10" s="255"/>
+      <c r="P10" s="255"/>
+      <c r="Q10" s="256"/>
+      <c r="S10" s="289" t="s">
         <v>17</v>
       </c>
-      <c r="T10" s="216"/>
-      <c r="U10" s="216"/>
-      <c r="V10" s="216"/>
-      <c r="Y10" s="236" t="s">
+      <c r="T10" s="289"/>
+      <c r="U10" s="289"/>
+      <c r="V10" s="289"/>
+      <c r="Y10" s="267" t="s">
         <v>18</v>
       </c>
-      <c r="Z10" s="239" t="s">
+      <c r="Z10" s="270" t="s">
         <v>19</v>
       </c>
       <c r="AA10" s="101"/>
-      <c r="AB10" s="226" t="s">
+      <c r="AB10" s="257" t="s">
         <v>20</v>
       </c>
-      <c r="AC10" s="242" t="s">
+      <c r="AC10" s="273" t="s">
         <v>21</v>
       </c>
-      <c r="AD10" s="245" t="s">
+      <c r="AD10" s="276" t="s">
         <v>84</v>
       </c>
-      <c r="AE10" s="226" t="s">
+      <c r="AE10" s="257" t="s">
         <v>22</v>
       </c>
-      <c r="AG10" s="226" t="s">
+      <c r="AG10" s="257" t="s">
         <v>23</v>
       </c>
       <c r="AH10" s="101"/>
-      <c r="AI10" s="226" t="s">
+      <c r="AI10" s="257" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="11" spans="2:35" s="100" customFormat="1" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="218"/>
-      <c r="C11" s="221"/>
-      <c r="D11" s="221"/>
-      <c r="E11" s="221"/>
-      <c r="F11" s="230" t="s">
+      <c r="B11" s="249"/>
+      <c r="C11" s="252"/>
+      <c r="D11" s="252"/>
+      <c r="E11" s="252"/>
+      <c r="F11" s="261" t="s">
         <v>25</v>
       </c>
-      <c r="G11" s="230" t="s">
+      <c r="G11" s="261" t="s">
         <v>26</v>
       </c>
-      <c r="H11" s="230" t="s">
+      <c r="H11" s="261" t="s">
         <v>27</v>
       </c>
-      <c r="I11" s="231" t="s">
+      <c r="I11" s="262" t="s">
         <v>28</v>
       </c>
-      <c r="J11" s="231" t="s">
+      <c r="J11" s="262" t="s">
         <v>29</v>
       </c>
-      <c r="K11" s="231" t="s">
+      <c r="K11" s="262" t="s">
         <v>30</v>
       </c>
-      <c r="L11" s="231" t="s">
+      <c r="L11" s="262" t="s">
         <v>31</v>
       </c>
-      <c r="M11" s="233" t="s">
+      <c r="M11" s="264" t="s">
         <v>32</v>
       </c>
-      <c r="N11" s="234"/>
-      <c r="O11" s="234"/>
-      <c r="P11" s="234"/>
-      <c r="Q11" s="235"/>
-      <c r="S11" s="216" t="s">
+      <c r="N11" s="265"/>
+      <c r="O11" s="265"/>
+      <c r="P11" s="265"/>
+      <c r="Q11" s="266"/>
+      <c r="S11" s="289" t="s">
         <v>33</v>
       </c>
-      <c r="T11" s="216"/>
-      <c r="U11" s="216"/>
-      <c r="V11" s="216"/>
-      <c r="Y11" s="237"/>
-      <c r="Z11" s="240"/>
+      <c r="T11" s="289"/>
+      <c r="U11" s="289"/>
+      <c r="V11" s="289"/>
+      <c r="Y11" s="268"/>
+      <c r="Z11" s="271"/>
       <c r="AA11" s="101"/>
-      <c r="AB11" s="227"/>
-      <c r="AC11" s="243"/>
-      <c r="AD11" s="246"/>
-      <c r="AE11" s="227"/>
-      <c r="AG11" s="227"/>
+      <c r="AB11" s="258"/>
+      <c r="AC11" s="274"/>
+      <c r="AD11" s="277"/>
+      <c r="AE11" s="258"/>
+      <c r="AG11" s="258"/>
       <c r="AH11" s="101"/>
-      <c r="AI11" s="227"/>
+      <c r="AI11" s="258"/>
     </row>
     <row r="12" spans="2:35" s="102" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="219"/>
-      <c r="C12" s="222"/>
-      <c r="D12" s="222"/>
-      <c r="E12" s="222"/>
-      <c r="F12" s="222"/>
-      <c r="G12" s="222"/>
-      <c r="H12" s="222"/>
-      <c r="I12" s="232"/>
-      <c r="J12" s="232"/>
-      <c r="K12" s="232"/>
-      <c r="L12" s="232"/>
+      <c r="B12" s="250"/>
+      <c r="C12" s="253"/>
+      <c r="D12" s="253"/>
+      <c r="E12" s="253"/>
+      <c r="F12" s="253"/>
+      <c r="G12" s="253"/>
+      <c r="H12" s="253"/>
+      <c r="I12" s="263"/>
+      <c r="J12" s="263"/>
+      <c r="K12" s="263"/>
+      <c r="L12" s="263"/>
       <c r="M12" s="4" t="s">
         <v>34</v>
       </c>
@@ -3354,20 +3373,20 @@
       <c r="T12" s="188" t="s">
         <v>35</v>
       </c>
-      <c r="U12" s="248" t="s">
+      <c r="U12" s="279" t="s">
         <v>36</v>
       </c>
-      <c r="V12" s="248"/>
-      <c r="Y12" s="238"/>
-      <c r="Z12" s="241"/>
+      <c r="V12" s="279"/>
+      <c r="Y12" s="269"/>
+      <c r="Z12" s="272"/>
       <c r="AA12" s="101"/>
-      <c r="AB12" s="229"/>
-      <c r="AC12" s="244"/>
-      <c r="AD12" s="247"/>
-      <c r="AE12" s="229"/>
-      <c r="AG12" s="228"/>
+      <c r="AB12" s="260"/>
+      <c r="AC12" s="275"/>
+      <c r="AD12" s="278"/>
+      <c r="AE12" s="260"/>
+      <c r="AG12" s="259"/>
       <c r="AH12" s="101"/>
-      <c r="AI12" s="229"/>
+      <c r="AI12" s="260"/>
     </row>
     <row r="13" spans="2:35" s="102" customFormat="1" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="103" t="s">
@@ -3397,8 +3416,8 @@
       <c r="Q13" s="13"/>
       <c r="S13" s="14"/>
       <c r="T13" s="189"/>
-      <c r="U13" s="202"/>
-      <c r="V13" s="202"/>
+      <c r="U13" s="283"/>
+      <c r="V13" s="283"/>
       <c r="Y13" s="105">
         <f>F13*C13</f>
         <v>0</v>
@@ -3461,8 +3480,8 @@
       <c r="Q14" s="22"/>
       <c r="S14" s="23"/>
       <c r="T14" s="23"/>
-      <c r="U14" s="197"/>
-      <c r="V14" s="197"/>
+      <c r="U14" s="284"/>
+      <c r="V14" s="284"/>
       <c r="Y14" s="115">
         <f t="shared" ref="Y14:Y71" si="3">F14*C14</f>
         <v>0</v>
@@ -3525,8 +3544,8 @@
       <c r="Q15" s="22"/>
       <c r="S15" s="23"/>
       <c r="T15" s="23"/>
-      <c r="U15" s="197"/>
-      <c r="V15" s="197"/>
+      <c r="U15" s="284"/>
+      <c r="V15" s="284"/>
       <c r="Y15" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -3589,8 +3608,8 @@
       <c r="Q16" s="22"/>
       <c r="S16" s="23"/>
       <c r="T16" s="23"/>
-      <c r="U16" s="198"/>
-      <c r="V16" s="198"/>
+      <c r="U16" s="290"/>
+      <c r="V16" s="290"/>
       <c r="Y16" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -3653,8 +3672,8 @@
       <c r="Q17" s="22"/>
       <c r="S17" s="23"/>
       <c r="T17" s="26"/>
-      <c r="U17" s="200"/>
-      <c r="V17" s="200"/>
+      <c r="U17" s="292"/>
+      <c r="V17" s="292"/>
       <c r="Y17" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -3717,8 +3736,8 @@
       <c r="Q18" s="22"/>
       <c r="S18" s="23"/>
       <c r="T18" s="26"/>
-      <c r="U18" s="200"/>
-      <c r="V18" s="200"/>
+      <c r="U18" s="292"/>
+      <c r="V18" s="292"/>
       <c r="Y18" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -3781,8 +3800,8 @@
       <c r="Q19" s="33"/>
       <c r="S19" s="34"/>
       <c r="T19" s="35"/>
-      <c r="U19" s="204"/>
-      <c r="V19" s="204"/>
+      <c r="U19" s="291"/>
+      <c r="V19" s="291"/>
       <c r="Y19" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -3845,8 +3864,8 @@
       <c r="Q20" s="22"/>
       <c r="S20" s="23"/>
       <c r="T20" s="26"/>
-      <c r="U20" s="198"/>
-      <c r="V20" s="198"/>
+      <c r="U20" s="290"/>
+      <c r="V20" s="290"/>
       <c r="Y20" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -3909,8 +3928,8 @@
       <c r="Q21" s="33"/>
       <c r="S21" s="34"/>
       <c r="T21" s="35"/>
-      <c r="U21" s="204"/>
-      <c r="V21" s="204"/>
+      <c r="U21" s="291"/>
+      <c r="V21" s="291"/>
       <c r="Y21" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -3973,8 +3992,8 @@
       <c r="Q22" s="42"/>
       <c r="S22" s="43"/>
       <c r="T22" s="44"/>
-      <c r="U22" s="198"/>
-      <c r="V22" s="198"/>
+      <c r="U22" s="290"/>
+      <c r="V22" s="290"/>
       <c r="Y22" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -4037,8 +4056,8 @@
       <c r="Q23" s="22"/>
       <c r="S23" s="23"/>
       <c r="T23" s="26"/>
-      <c r="U23" s="200"/>
-      <c r="V23" s="200"/>
+      <c r="U23" s="292"/>
+      <c r="V23" s="292"/>
       <c r="Y23" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -4101,8 +4120,8 @@
       <c r="Q24" s="22"/>
       <c r="S24" s="23"/>
       <c r="T24" s="26"/>
-      <c r="U24" s="197"/>
-      <c r="V24" s="197"/>
+      <c r="U24" s="284"/>
+      <c r="V24" s="284"/>
       <c r="Y24" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -4165,8 +4184,8 @@
       <c r="Q25" s="33"/>
       <c r="S25" s="34"/>
       <c r="T25" s="35"/>
-      <c r="U25" s="200"/>
-      <c r="V25" s="200"/>
+      <c r="U25" s="292"/>
+      <c r="V25" s="292"/>
       <c r="Y25" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -4229,8 +4248,8 @@
       <c r="Q26" s="42"/>
       <c r="S26" s="43"/>
       <c r="T26" s="44"/>
-      <c r="U26" s="203"/>
-      <c r="V26" s="203"/>
+      <c r="U26" s="293"/>
+      <c r="V26" s="293"/>
       <c r="Y26" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -4293,8 +4312,8 @@
       <c r="Q27" s="33"/>
       <c r="S27" s="34"/>
       <c r="T27" s="35"/>
-      <c r="U27" s="198"/>
-      <c r="V27" s="198"/>
+      <c r="U27" s="290"/>
+      <c r="V27" s="290"/>
       <c r="Y27" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -4357,8 +4376,8 @@
       <c r="Q28" s="42"/>
       <c r="S28" s="43"/>
       <c r="T28" s="44"/>
-      <c r="U28" s="203"/>
-      <c r="V28" s="203"/>
+      <c r="U28" s="293"/>
+      <c r="V28" s="293"/>
       <c r="Y28" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -4421,8 +4440,8 @@
       <c r="Q29" s="22"/>
       <c r="S29" s="23"/>
       <c r="T29" s="26"/>
-      <c r="U29" s="198"/>
-      <c r="V29" s="198"/>
+      <c r="U29" s="290"/>
+      <c r="V29" s="290"/>
       <c r="Y29" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -4483,8 +4502,8 @@
       <c r="Q30" s="22"/>
       <c r="S30" s="23"/>
       <c r="T30" s="26"/>
-      <c r="U30" s="197"/>
-      <c r="V30" s="197"/>
+      <c r="U30" s="284"/>
+      <c r="V30" s="284"/>
       <c r="Y30" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -4545,8 +4564,8 @@
       <c r="Q31" s="22"/>
       <c r="S31" s="26"/>
       <c r="T31" s="26"/>
-      <c r="U31" s="200"/>
-      <c r="V31" s="200"/>
+      <c r="U31" s="292"/>
+      <c r="V31" s="292"/>
       <c r="Y31" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -4607,8 +4626,8 @@
       <c r="Q32" s="22"/>
       <c r="S32" s="26"/>
       <c r="T32" s="26"/>
-      <c r="U32" s="197"/>
-      <c r="V32" s="197"/>
+      <c r="U32" s="284"/>
+      <c r="V32" s="284"/>
       <c r="Y32" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -4664,8 +4683,8 @@
       <c r="Q33" s="22"/>
       <c r="S33" s="26"/>
       <c r="T33" s="26"/>
-      <c r="U33" s="197"/>
-      <c r="V33" s="197"/>
+      <c r="U33" s="284"/>
+      <c r="V33" s="284"/>
       <c r="Y33" s="115"/>
       <c r="Z33" s="116"/>
       <c r="AA33" s="107"/>
@@ -4704,8 +4723,8 @@
       <c r="Q34" s="22"/>
       <c r="S34" s="26"/>
       <c r="T34" s="26"/>
-      <c r="U34" s="197"/>
-      <c r="V34" s="197"/>
+      <c r="U34" s="284"/>
+      <c r="V34" s="284"/>
       <c r="Y34" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -4766,8 +4785,8 @@
       <c r="Q35" s="22"/>
       <c r="S35" s="26"/>
       <c r="T35" s="26"/>
-      <c r="U35" s="197"/>
-      <c r="V35" s="197"/>
+      <c r="U35" s="284"/>
+      <c r="V35" s="284"/>
       <c r="Y35" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -4828,8 +4847,8 @@
       <c r="Q36" s="33"/>
       <c r="S36" s="35"/>
       <c r="T36" s="35"/>
-      <c r="U36" s="198"/>
-      <c r="V36" s="198"/>
+      <c r="U36" s="290"/>
+      <c r="V36" s="290"/>
       <c r="Y36" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -4890,8 +4909,8 @@
       <c r="Q37" s="42"/>
       <c r="S37" s="44"/>
       <c r="T37" s="44"/>
-      <c r="U37" s="203"/>
-      <c r="V37" s="203"/>
+      <c r="U37" s="293"/>
+      <c r="V37" s="293"/>
       <c r="Y37" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -4952,8 +4971,8 @@
       <c r="Q38" s="22"/>
       <c r="S38" s="26"/>
       <c r="T38" s="26"/>
-      <c r="U38" s="198"/>
-      <c r="V38" s="198"/>
+      <c r="U38" s="290"/>
+      <c r="V38" s="290"/>
       <c r="Y38" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -5014,8 +5033,8 @@
       <c r="Q39" s="33"/>
       <c r="S39" s="35"/>
       <c r="T39" s="35"/>
-      <c r="U39" s="204"/>
-      <c r="V39" s="204"/>
+      <c r="U39" s="291"/>
+      <c r="V39" s="291"/>
       <c r="Y39" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -5076,8 +5095,8 @@
       <c r="Q40" s="42"/>
       <c r="S40" s="44"/>
       <c r="T40" s="44"/>
-      <c r="U40" s="198"/>
-      <c r="V40" s="198"/>
+      <c r="U40" s="290"/>
+      <c r="V40" s="290"/>
       <c r="Y40" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -5138,8 +5157,8 @@
       <c r="Q41" s="22"/>
       <c r="S41" s="26"/>
       <c r="T41" s="26"/>
-      <c r="U41" s="200"/>
-      <c r="V41" s="200"/>
+      <c r="U41" s="292"/>
+      <c r="V41" s="292"/>
       <c r="Y41" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -5200,8 +5219,8 @@
       <c r="Q42" s="22"/>
       <c r="S42" s="26"/>
       <c r="T42" s="26"/>
-      <c r="U42" s="200"/>
-      <c r="V42" s="200"/>
+      <c r="U42" s="292"/>
+      <c r="V42" s="292"/>
       <c r="Y42" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -5257,8 +5276,8 @@
       <c r="Q43" s="33"/>
       <c r="S43" s="35"/>
       <c r="T43" s="35"/>
-      <c r="U43" s="204"/>
-      <c r="V43" s="204"/>
+      <c r="U43" s="291"/>
+      <c r="V43" s="291"/>
       <c r="Y43" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -5312,8 +5331,8 @@
       <c r="Q44" s="22"/>
       <c r="S44" s="23"/>
       <c r="T44" s="26"/>
-      <c r="U44" s="201"/>
-      <c r="V44" s="201"/>
+      <c r="U44" s="294"/>
+      <c r="V44" s="294"/>
       <c r="Y44" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -5364,8 +5383,8 @@
       <c r="Q45" s="22"/>
       <c r="S45" s="23"/>
       <c r="T45" s="26"/>
-      <c r="U45" s="195"/>
-      <c r="V45" s="195"/>
+      <c r="U45" s="295"/>
+      <c r="V45" s="295"/>
       <c r="Y45" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -5416,8 +5435,8 @@
       <c r="Q46" s="33"/>
       <c r="S46" s="34"/>
       <c r="T46" s="35"/>
-      <c r="U46" s="202"/>
-      <c r="V46" s="202"/>
+      <c r="U46" s="283"/>
+      <c r="V46" s="283"/>
       <c r="Y46" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -5465,8 +5484,8 @@
       <c r="Q47" s="174"/>
       <c r="S47" s="171"/>
       <c r="T47" s="172"/>
-      <c r="U47" s="203"/>
-      <c r="V47" s="203"/>
+      <c r="U47" s="293"/>
+      <c r="V47" s="293"/>
       <c r="Y47" s="115"/>
       <c r="Z47" s="116"/>
       <c r="AA47" s="107"/>
@@ -5507,8 +5526,8 @@
       <c r="Q48" s="22"/>
       <c r="S48" s="23"/>
       <c r="T48" s="26"/>
-      <c r="U48" s="197"/>
-      <c r="V48" s="197"/>
+      <c r="U48" s="284"/>
+      <c r="V48" s="284"/>
       <c r="Y48" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -5569,8 +5588,8 @@
       <c r="Q49" s="22"/>
       <c r="S49" s="26"/>
       <c r="T49" s="26"/>
-      <c r="U49" s="197"/>
-      <c r="V49" s="197"/>
+      <c r="U49" s="284"/>
+      <c r="V49" s="284"/>
       <c r="Y49" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -5633,8 +5652,8 @@
       <c r="Q50" s="22"/>
       <c r="S50" s="23"/>
       <c r="T50" s="26"/>
-      <c r="U50" s="197"/>
-      <c r="V50" s="197"/>
+      <c r="U50" s="284"/>
+      <c r="V50" s="284"/>
       <c r="Y50" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -5697,8 +5716,8 @@
       <c r="Q51" s="57"/>
       <c r="S51" s="58"/>
       <c r="T51" s="58"/>
-      <c r="U51" s="201"/>
-      <c r="V51" s="201"/>
+      <c r="U51" s="294"/>
+      <c r="V51" s="294"/>
       <c r="Y51" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -5757,8 +5776,8 @@
       <c r="Q52" s="42"/>
       <c r="S52" s="44"/>
       <c r="T52" s="44"/>
-      <c r="U52" s="195"/>
-      <c r="V52" s="195"/>
+      <c r="U52" s="295"/>
+      <c r="V52" s="295"/>
       <c r="Y52" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -5817,8 +5836,8 @@
       <c r="Q53" s="22"/>
       <c r="S53" s="23"/>
       <c r="T53" s="23"/>
-      <c r="U53" s="202"/>
-      <c r="V53" s="202"/>
+      <c r="U53" s="283"/>
+      <c r="V53" s="283"/>
       <c r="Y53" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -5871,8 +5890,8 @@
       <c r="Q54" s="22"/>
       <c r="S54" s="23"/>
       <c r="T54" s="23"/>
-      <c r="U54" s="200"/>
-      <c r="V54" s="200"/>
+      <c r="U54" s="292"/>
+      <c r="V54" s="292"/>
       <c r="Y54" s="115"/>
       <c r="Z54" s="116"/>
       <c r="AA54" s="107"/>
@@ -5906,8 +5925,8 @@
       <c r="Q55" s="22"/>
       <c r="S55" s="23"/>
       <c r="T55" s="23"/>
-      <c r="U55" s="200"/>
-      <c r="V55" s="200"/>
+      <c r="U55" s="292"/>
+      <c r="V55" s="292"/>
       <c r="Y55" s="115"/>
       <c r="Z55" s="116"/>
       <c r="AA55" s="107"/>
@@ -5941,8 +5960,8 @@
       <c r="Q56" s="22"/>
       <c r="S56" s="23"/>
       <c r="T56" s="23"/>
-      <c r="U56" s="197"/>
-      <c r="V56" s="197"/>
+      <c r="U56" s="284"/>
+      <c r="V56" s="284"/>
       <c r="Y56" s="115"/>
       <c r="Z56" s="116"/>
       <c r="AA56" s="107"/>
@@ -5983,8 +6002,8 @@
       <c r="Q57" s="22"/>
       <c r="S57" s="23"/>
       <c r="T57" s="26"/>
-      <c r="U57" s="198"/>
-      <c r="V57" s="198"/>
+      <c r="U57" s="290"/>
+      <c r="V57" s="290"/>
       <c r="Y57" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -6037,8 +6056,8 @@
       <c r="Q58" s="22"/>
       <c r="S58" s="23"/>
       <c r="T58" s="26"/>
-      <c r="U58" s="200"/>
-      <c r="V58" s="200"/>
+      <c r="U58" s="292"/>
+      <c r="V58" s="292"/>
       <c r="Y58" s="115"/>
       <c r="Z58" s="116"/>
       <c r="AA58" s="107"/>
@@ -6072,8 +6091,8 @@
       <c r="Q59" s="22"/>
       <c r="S59" s="23"/>
       <c r="T59" s="26"/>
-      <c r="U59" s="200"/>
-      <c r="V59" s="200"/>
+      <c r="U59" s="292"/>
+      <c r="V59" s="292"/>
       <c r="Y59" s="115"/>
       <c r="Z59" s="116"/>
       <c r="AA59" s="107"/>
@@ -6107,8 +6126,8 @@
       <c r="Q60" s="22"/>
       <c r="S60" s="23"/>
       <c r="T60" s="26"/>
-      <c r="U60" s="197"/>
-      <c r="V60" s="197"/>
+      <c r="U60" s="284"/>
+      <c r="V60" s="284"/>
       <c r="Y60" s="115"/>
       <c r="Z60" s="116"/>
       <c r="AA60" s="107"/>
@@ -6140,8 +6159,8 @@
       <c r="Q61" s="22"/>
       <c r="S61" s="23"/>
       <c r="T61" s="26"/>
-      <c r="U61" s="198"/>
-      <c r="V61" s="198"/>
+      <c r="U61" s="290"/>
+      <c r="V61" s="290"/>
       <c r="Y61" s="115"/>
       <c r="Z61" s="116"/>
       <c r="AA61" s="107"/>
@@ -6180,8 +6199,8 @@
       <c r="Q62" s="22"/>
       <c r="S62" s="180"/>
       <c r="T62" s="59"/>
-      <c r="U62" s="199"/>
-      <c r="V62" s="199"/>
+      <c r="U62" s="296"/>
+      <c r="V62" s="296"/>
       <c r="Y62" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -6241,8 +6260,8 @@
       <c r="Q63" s="22"/>
       <c r="S63" s="43"/>
       <c r="T63" s="44"/>
-      <c r="U63" s="195"/>
-      <c r="V63" s="195"/>
+      <c r="U63" s="295"/>
+      <c r="V63" s="295"/>
       <c r="Y63" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -6301,8 +6320,8 @@
       <c r="Q64" s="33"/>
       <c r="S64" s="34"/>
       <c r="T64" s="35"/>
-      <c r="U64" s="195"/>
-      <c r="V64" s="195"/>
+      <c r="U64" s="295"/>
+      <c r="V64" s="295"/>
       <c r="Y64" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -6360,8 +6379,8 @@
       <c r="Q65" s="42"/>
       <c r="S65" s="44"/>
       <c r="T65" s="44"/>
-      <c r="U65" s="195"/>
-      <c r="V65" s="195"/>
+      <c r="U65" s="295"/>
+      <c r="V65" s="295"/>
       <c r="Y65" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -6422,8 +6441,8 @@
       <c r="Q66" s="22"/>
       <c r="S66" s="26"/>
       <c r="T66" s="26"/>
-      <c r="U66" s="195"/>
-      <c r="V66" s="195"/>
+      <c r="U66" s="295"/>
+      <c r="V66" s="295"/>
       <c r="Y66" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -6484,8 +6503,8 @@
       <c r="Q67" s="22"/>
       <c r="S67" s="26"/>
       <c r="T67" s="26"/>
-      <c r="U67" s="195"/>
-      <c r="V67" s="195"/>
+      <c r="U67" s="295"/>
+      <c r="V67" s="295"/>
       <c r="Y67" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -6546,8 +6565,8 @@
       <c r="Q68" s="22"/>
       <c r="S68" s="26"/>
       <c r="T68" s="26"/>
-      <c r="U68" s="195"/>
-      <c r="V68" s="195"/>
+      <c r="U68" s="295"/>
+      <c r="V68" s="295"/>
       <c r="Y68" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -6608,8 +6627,8 @@
       <c r="Q69" s="22"/>
       <c r="S69" s="26"/>
       <c r="T69" s="26"/>
-      <c r="U69" s="195"/>
-      <c r="V69" s="195"/>
+      <c r="U69" s="295"/>
+      <c r="V69" s="295"/>
       <c r="Y69" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -6670,8 +6689,8 @@
       <c r="Q70" s="22"/>
       <c r="S70" s="26"/>
       <c r="T70" s="26"/>
-      <c r="U70" s="195"/>
-      <c r="V70" s="195"/>
+      <c r="U70" s="295"/>
+      <c r="V70" s="295"/>
       <c r="Y70" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -6732,8 +6751,8 @@
       <c r="Q71" s="57"/>
       <c r="S71" s="58"/>
       <c r="T71" s="58"/>
-      <c r="U71" s="195"/>
-      <c r="V71" s="195"/>
+      <c r="U71" s="295"/>
+      <c r="V71" s="295"/>
       <c r="Y71" s="131">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -6810,8 +6829,8 @@
       </c>
       <c r="S72" s="64"/>
       <c r="T72" s="64"/>
-      <c r="U72" s="195"/>
-      <c r="V72" s="195"/>
+      <c r="U72" s="295"/>
+      <c r="V72" s="295"/>
       <c r="AB72" s="102">
         <v>0.61</v>
       </c>
@@ -6858,21 +6877,21 @@
       </c>
       <c r="S73" s="70"/>
       <c r="T73" s="70"/>
-      <c r="U73" s="195"/>
-      <c r="V73" s="195"/>
+      <c r="U73" s="295"/>
+      <c r="V73" s="295"/>
       <c r="AB73" s="102">
         <v>0.61</v>
       </c>
     </row>
     <row r="74" spans="2:35" s="102" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B74" s="249" t="s">
+      <c r="B74" s="233" t="s">
         <v>55</v>
       </c>
-      <c r="C74" s="249"/>
-      <c r="D74" s="249"/>
-      <c r="E74" s="249"/>
-      <c r="F74" s="249"/>
-      <c r="G74" s="249"/>
+      <c r="C74" s="233"/>
+      <c r="D74" s="233"/>
+      <c r="E74" s="233"/>
+      <c r="F74" s="233"/>
+      <c r="G74" s="233"/>
       <c r="H74" s="72" t="str">
         <f>ROUND(((F13+F28+F52+F53+F57+F62+F63+F64)/72+(F14+F17+F18)/108+(F15+SUM(F19:F27)+F29+F30+F48+F50+F42)/63+F16/96+SUM(F31:F41)/100+SUM(F44:F46)/24+SUM(F65:F71)/100+(F51+F43+F49)/100),1)&amp;" pallets"</f>
         <v>0 pallets</v>
@@ -6948,27 +6967,27 @@
       <c r="C76" s="142"/>
       <c r="D76" s="142"/>
       <c r="E76" s="142"/>
-      <c r="F76" s="250"/>
-      <c r="G76" s="250"/>
-      <c r="H76" s="250"/>
-      <c r="I76" s="251"/>
+      <c r="F76" s="234"/>
+      <c r="G76" s="234"/>
+      <c r="H76" s="234"/>
+      <c r="I76" s="235"/>
       <c r="J76" s="77"/>
       <c r="K76" s="77"/>
       <c r="L76" s="77"/>
-      <c r="M76" s="252" t="s">
+      <c r="M76" s="236" t="s">
         <v>57</v>
       </c>
-      <c r="N76" s="253"/>
-      <c r="O76" s="250"/>
-      <c r="P76" s="250"/>
-      <c r="Q76" s="251"/>
+      <c r="N76" s="237"/>
+      <c r="O76" s="234"/>
+      <c r="P76" s="234"/>
+      <c r="Q76" s="235"/>
       <c r="R76" s="139"/>
-      <c r="S76" s="196" t="s">
+      <c r="S76" s="245" t="s">
         <v>58</v>
       </c>
-      <c r="T76" s="196"/>
-      <c r="U76" s="196"/>
-      <c r="V76" s="196"/>
+      <c r="T76" s="245"/>
+      <c r="U76" s="245"/>
+      <c r="V76" s="245"/>
       <c r="W76" s="78"/>
       <c r="X76" s="78"/>
       <c r="Y76" s="78"/>
@@ -7023,31 +7042,31 @@
       <c r="C78" s="142"/>
       <c r="D78" s="142"/>
       <c r="E78" s="142"/>
-      <c r="F78" s="250"/>
-      <c r="G78" s="250"/>
-      <c r="H78" s="250"/>
-      <c r="I78" s="251"/>
+      <c r="F78" s="234"/>
+      <c r="G78" s="234"/>
+      <c r="H78" s="234"/>
+      <c r="I78" s="235"/>
       <c r="J78" s="80"/>
       <c r="K78" s="80"/>
       <c r="L78" s="80"/>
-      <c r="M78" s="257" t="s">
+      <c r="M78" s="244" t="s">
         <v>60</v>
       </c>
-      <c r="N78" s="257"/>
+      <c r="N78" s="244"/>
       <c r="O78" s="82" t="s">
         <v>61</v>
       </c>
-      <c r="P78" s="256"/>
-      <c r="Q78" s="251"/>
+      <c r="P78" s="243"/>
+      <c r="Q78" s="235"/>
       <c r="R78" s="139"/>
-      <c r="S78" s="196" t="s">
+      <c r="S78" s="245" t="s">
         <v>62</v>
       </c>
-      <c r="T78" s="196"/>
-      <c r="U78" s="196"/>
-      <c r="V78" s="196"/>
+      <c r="T78" s="245"/>
+      <c r="U78" s="245"/>
+      <c r="V78" s="245"/>
       <c r="W78" s="78"/>
-      <c r="X78" s="209" t="s">
+      <c r="X78" s="238" t="s">
         <v>63</v>
       </c>
       <c r="Y78" s="78"/>
@@ -7082,7 +7101,7 @@
       <c r="U79" s="81"/>
       <c r="V79" s="81"/>
       <c r="W79" s="78"/>
-      <c r="X79" s="210"/>
+      <c r="X79" s="239"/>
       <c r="Y79" s="78"/>
       <c r="Z79" s="78"/>
       <c r="AA79" s="78"/>
@@ -7102,35 +7121,35 @@
       <c r="C80" s="142"/>
       <c r="D80" s="142"/>
       <c r="E80" s="142"/>
-      <c r="F80" s="250" t="str">
+      <c r="F80" s="234" t="str">
         <f>IF(U7&gt;0,"",F76-T80)</f>
         <v/>
       </c>
-      <c r="G80" s="250"/>
-      <c r="H80" s="250"/>
-      <c r="I80" s="251"/>
+      <c r="G80" s="234"/>
+      <c r="H80" s="234"/>
+      <c r="I80" s="235"/>
       <c r="J80" s="80"/>
       <c r="K80" s="80"/>
       <c r="L80" s="80"/>
-      <c r="M80" s="254" t="str">
+      <c r="M80" s="241" t="str">
         <f>IF(U7&gt;0,"",T5+30)</f>
         <v/>
       </c>
-      <c r="N80" s="255"/>
+      <c r="N80" s="242"/>
       <c r="O80" s="82" t="s">
         <v>65</v>
       </c>
-      <c r="P80" s="256"/>
-      <c r="Q80" s="251"/>
+      <c r="P80" s="243"/>
+      <c r="Q80" s="235"/>
       <c r="R80" s="139"/>
-      <c r="S80" s="258" t="s">
+      <c r="S80" s="246" t="s">
         <v>66</v>
       </c>
-      <c r="T80" s="259"/>
-      <c r="U80" s="259"/>
-      <c r="V80" s="259"/>
+      <c r="T80" s="247"/>
+      <c r="U80" s="247"/>
+      <c r="V80" s="247"/>
       <c r="W80" s="78"/>
-      <c r="X80" s="211"/>
+      <c r="X80" s="240"/>
       <c r="Y80" s="78"/>
       <c r="Z80" s="78"/>
       <c r="AA80" s="78"/>
@@ -7180,83 +7199,83 @@
       <c r="AI81" s="78"/>
     </row>
     <row r="82" spans="2:35" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B82" s="278" t="s">
+      <c r="B82" s="213" t="s">
         <v>67</v>
       </c>
-      <c r="C82" s="279"/>
-      <c r="D82" s="279"/>
-      <c r="E82" s="279"/>
-      <c r="F82" s="279"/>
-      <c r="G82" s="279"/>
-      <c r="H82" s="280"/>
-      <c r="I82" s="287" t="s">
+      <c r="C82" s="214"/>
+      <c r="D82" s="214"/>
+      <c r="E82" s="214"/>
+      <c r="F82" s="214"/>
+      <c r="G82" s="214"/>
+      <c r="H82" s="215"/>
+      <c r="I82" s="222" t="s">
         <v>68</v>
       </c>
       <c r="J82" s="148"/>
       <c r="K82" s="148"/>
       <c r="L82" s="148"/>
-      <c r="M82" s="289"/>
-      <c r="N82" s="292" t="s">
+      <c r="M82" s="224"/>
+      <c r="N82" s="227" t="s">
         <v>69</v>
       </c>
-      <c r="O82" s="295"/>
-      <c r="P82" s="289"/>
-      <c r="Q82" s="269" t="s">
+      <c r="O82" s="230"/>
+      <c r="P82" s="224"/>
+      <c r="Q82" s="204" t="s">
         <v>70</v>
       </c>
-      <c r="R82" s="270"/>
-      <c r="S82" s="275"/>
-      <c r="T82" s="269" t="s">
+      <c r="R82" s="205"/>
+      <c r="S82" s="210"/>
+      <c r="T82" s="204" t="s">
         <v>71</v>
       </c>
-      <c r="U82" s="215"/>
-      <c r="V82" s="215"/>
+      <c r="U82" s="194"/>
+      <c r="V82" s="194"/>
     </row>
     <row r="83" spans="2:35" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B83" s="281"/>
-      <c r="C83" s="282"/>
-      <c r="D83" s="282"/>
-      <c r="E83" s="282"/>
-      <c r="F83" s="282"/>
-      <c r="G83" s="282"/>
-      <c r="H83" s="283"/>
-      <c r="I83" s="263"/>
+      <c r="B83" s="216"/>
+      <c r="C83" s="217"/>
+      <c r="D83" s="217"/>
+      <c r="E83" s="217"/>
+      <c r="F83" s="217"/>
+      <c r="G83" s="217"/>
+      <c r="H83" s="218"/>
+      <c r="I83" s="198"/>
       <c r="J83" s="91"/>
       <c r="K83" s="91"/>
       <c r="L83" s="91"/>
-      <c r="M83" s="290"/>
-      <c r="N83" s="293"/>
-      <c r="O83" s="296"/>
-      <c r="P83" s="290"/>
-      <c r="Q83" s="271"/>
-      <c r="R83" s="272"/>
-      <c r="S83" s="276"/>
-      <c r="T83" s="271"/>
-      <c r="U83" s="215"/>
-      <c r="V83" s="215"/>
+      <c r="M83" s="225"/>
+      <c r="N83" s="228"/>
+      <c r="O83" s="231"/>
+      <c r="P83" s="225"/>
+      <c r="Q83" s="206"/>
+      <c r="R83" s="207"/>
+      <c r="S83" s="211"/>
+      <c r="T83" s="206"/>
+      <c r="U83" s="194"/>
+      <c r="V83" s="194"/>
     </row>
     <row r="84" spans="2:35" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B84" s="284"/>
-      <c r="C84" s="285"/>
-      <c r="D84" s="285"/>
-      <c r="E84" s="285"/>
-      <c r="F84" s="285"/>
-      <c r="G84" s="285"/>
-      <c r="H84" s="286"/>
-      <c r="I84" s="288"/>
+      <c r="B84" s="219"/>
+      <c r="C84" s="220"/>
+      <c r="D84" s="220"/>
+      <c r="E84" s="220"/>
+      <c r="F84" s="220"/>
+      <c r="G84" s="220"/>
+      <c r="H84" s="221"/>
+      <c r="I84" s="223"/>
       <c r="J84" s="149"/>
       <c r="K84" s="149"/>
       <c r="L84" s="149"/>
-      <c r="M84" s="291"/>
-      <c r="N84" s="294"/>
-      <c r="O84" s="297"/>
-      <c r="P84" s="291"/>
-      <c r="Q84" s="273"/>
-      <c r="R84" s="274"/>
-      <c r="S84" s="277"/>
-      <c r="T84" s="273"/>
-      <c r="U84" s="215"/>
-      <c r="V84" s="215"/>
+      <c r="M84" s="226"/>
+      <c r="N84" s="229"/>
+      <c r="O84" s="232"/>
+      <c r="P84" s="226"/>
+      <c r="Q84" s="208"/>
+      <c r="R84" s="209"/>
+      <c r="S84" s="212"/>
+      <c r="T84" s="208"/>
+      <c r="U84" s="194"/>
+      <c r="V84" s="194"/>
     </row>
     <row r="85" spans="2:35" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="V85" s="190"/>
@@ -7318,22 +7337,22 @@
       <c r="V88" s="157"/>
     </row>
     <row r="89" spans="2:35" s="156" customFormat="1" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="B89" s="266"/>
-      <c r="C89" s="267"/>
-      <c r="D89" s="267"/>
-      <c r="E89" s="267"/>
-      <c r="F89" s="267"/>
-      <c r="G89" s="267"/>
-      <c r="H89" s="267"/>
-      <c r="I89" s="268"/>
+      <c r="B89" s="201"/>
+      <c r="C89" s="202"/>
+      <c r="D89" s="202"/>
+      <c r="E89" s="202"/>
+      <c r="F89" s="202"/>
+      <c r="G89" s="202"/>
+      <c r="H89" s="202"/>
+      <c r="I89" s="203"/>
       <c r="J89" s="88"/>
       <c r="K89" s="88"/>
       <c r="L89" s="88"/>
-      <c r="M89" s="266"/>
-      <c r="N89" s="267"/>
-      <c r="O89" s="267"/>
-      <c r="P89" s="267"/>
-      <c r="Q89" s="268"/>
+      <c r="M89" s="201"/>
+      <c r="N89" s="202"/>
+      <c r="O89" s="202"/>
+      <c r="P89" s="202"/>
+      <c r="Q89" s="203"/>
       <c r="R89" s="158"/>
       <c r="S89" s="159"/>
       <c r="T89" s="159"/>
@@ -7342,29 +7361,29 @@
       <c r="W89" s="155"/>
     </row>
     <row r="90" spans="2:35" ht="18" x14ac:dyDescent="0.25">
-      <c r="B90" s="260" t="s">
+      <c r="B90" s="195" t="s">
         <v>76</v>
       </c>
-      <c r="C90" s="261"/>
-      <c r="D90" s="261"/>
-      <c r="E90" s="261"/>
-      <c r="F90" s="261"/>
-      <c r="G90" s="261"/>
-      <c r="H90" s="261"/>
-      <c r="I90" s="262"/>
-      <c r="M90" s="260" t="s">
+      <c r="C90" s="196"/>
+      <c r="D90" s="196"/>
+      <c r="E90" s="196"/>
+      <c r="F90" s="196"/>
+      <c r="G90" s="196"/>
+      <c r="H90" s="196"/>
+      <c r="I90" s="197"/>
+      <c r="M90" s="195" t="s">
         <v>76</v>
       </c>
-      <c r="N90" s="261"/>
-      <c r="O90" s="261"/>
-      <c r="P90" s="261"/>
-      <c r="Q90" s="262"/>
-      <c r="R90" s="263" t="s">
+      <c r="N90" s="196"/>
+      <c r="O90" s="196"/>
+      <c r="P90" s="196"/>
+      <c r="Q90" s="197"/>
+      <c r="R90" s="198" t="s">
         <v>77</v>
       </c>
-      <c r="S90" s="264"/>
-      <c r="T90" s="264"/>
-      <c r="U90" s="265"/>
+      <c r="S90" s="199"/>
+      <c r="T90" s="199"/>
+      <c r="U90" s="200"/>
       <c r="V90" s="192"/>
       <c r="W90" s="153"/>
     </row>
@@ -7405,16 +7424,16 @@
       <c r="V93" s="154"/>
     </row>
     <row r="94" spans="2:35" s="156" customFormat="1" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="B94" s="266" t="s">
+      <c r="B94" s="201" t="s">
         <v>87</v>
       </c>
-      <c r="C94" s="267"/>
-      <c r="D94" s="267"/>
-      <c r="E94" s="267"/>
-      <c r="F94" s="267"/>
-      <c r="G94" s="267"/>
-      <c r="H94" s="267"/>
-      <c r="I94" s="268"/>
+      <c r="C94" s="202"/>
+      <c r="D94" s="202"/>
+      <c r="E94" s="202"/>
+      <c r="F94" s="202"/>
+      <c r="G94" s="202"/>
+      <c r="H94" s="202"/>
+      <c r="I94" s="203"/>
       <c r="J94" s="88"/>
       <c r="K94" s="88"/>
       <c r="L94" s="88"/>
@@ -7433,24 +7452,24 @@
       <c r="W94" s="155"/>
     </row>
     <row r="95" spans="2:35" ht="18" x14ac:dyDescent="0.25">
-      <c r="B95" s="260" t="s">
+      <c r="B95" s="195" t="s">
         <v>80</v>
       </c>
-      <c r="C95" s="261"/>
-      <c r="D95" s="261"/>
-      <c r="E95" s="261"/>
-      <c r="F95" s="261"/>
-      <c r="G95" s="261"/>
-      <c r="H95" s="261"/>
-      <c r="I95" s="262"/>
+      <c r="C95" s="196"/>
+      <c r="D95" s="196"/>
+      <c r="E95" s="196"/>
+      <c r="F95" s="196"/>
+      <c r="G95" s="196"/>
+      <c r="H95" s="196"/>
+      <c r="I95" s="197"/>
       <c r="M95" s="153"/>
       <c r="Q95" s="86"/>
-      <c r="R95" s="263" t="s">
+      <c r="R95" s="198" t="s">
         <v>81</v>
       </c>
-      <c r="S95" s="264"/>
-      <c r="T95" s="264"/>
-      <c r="U95" s="265"/>
+      <c r="S95" s="199"/>
+      <c r="T95" s="199"/>
+      <c r="U95" s="200"/>
       <c r="V95" s="164"/>
     </row>
     <row r="96" spans="2:35" ht="12.75" x14ac:dyDescent="0.25">
@@ -7492,36 +7511,80 @@
     <row r="103" spans="2:23" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="126">
-    <mergeCell ref="U82:V84"/>
-    <mergeCell ref="B90:I90"/>
-    <mergeCell ref="M90:Q90"/>
-    <mergeCell ref="R90:U90"/>
-    <mergeCell ref="B94:I94"/>
-    <mergeCell ref="B95:I95"/>
-    <mergeCell ref="R95:U95"/>
-    <mergeCell ref="Q82:R84"/>
-    <mergeCell ref="S82:S84"/>
-    <mergeCell ref="T82:T84"/>
-    <mergeCell ref="B89:I89"/>
-    <mergeCell ref="M89:Q89"/>
-    <mergeCell ref="B82:H84"/>
-    <mergeCell ref="I82:I84"/>
-    <mergeCell ref="M82:M84"/>
-    <mergeCell ref="N82:N84"/>
-    <mergeCell ref="O82:P84"/>
-    <mergeCell ref="B74:G74"/>
-    <mergeCell ref="F76:I76"/>
-    <mergeCell ref="M76:N76"/>
-    <mergeCell ref="O76:Q76"/>
-    <mergeCell ref="X78:X80"/>
-    <mergeCell ref="F80:I80"/>
-    <mergeCell ref="M80:N80"/>
-    <mergeCell ref="P80:Q80"/>
-    <mergeCell ref="F78:I78"/>
-    <mergeCell ref="M78:N78"/>
-    <mergeCell ref="P78:Q78"/>
-    <mergeCell ref="S78:V78"/>
-    <mergeCell ref="S80:V80"/>
+    <mergeCell ref="U70:V70"/>
+    <mergeCell ref="U71:V71"/>
+    <mergeCell ref="U72:V72"/>
+    <mergeCell ref="U73:V73"/>
+    <mergeCell ref="S76:V76"/>
+    <mergeCell ref="U65:V65"/>
+    <mergeCell ref="U66:V66"/>
+    <mergeCell ref="U67:V67"/>
+    <mergeCell ref="U68:V68"/>
+    <mergeCell ref="U69:V69"/>
+    <mergeCell ref="U60:V60"/>
+    <mergeCell ref="U61:V61"/>
+    <mergeCell ref="U62:V62"/>
+    <mergeCell ref="U63:V63"/>
+    <mergeCell ref="U64:V64"/>
+    <mergeCell ref="U55:V55"/>
+    <mergeCell ref="U56:V56"/>
+    <mergeCell ref="U57:V57"/>
+    <mergeCell ref="U58:V58"/>
+    <mergeCell ref="U59:V59"/>
+    <mergeCell ref="U50:V50"/>
+    <mergeCell ref="U51:V51"/>
+    <mergeCell ref="U52:V52"/>
+    <mergeCell ref="U53:V53"/>
+    <mergeCell ref="U54:V54"/>
+    <mergeCell ref="U45:V45"/>
+    <mergeCell ref="U46:V46"/>
+    <mergeCell ref="U47:V47"/>
+    <mergeCell ref="U48:V48"/>
+    <mergeCell ref="U49:V49"/>
+    <mergeCell ref="U40:V40"/>
+    <mergeCell ref="U41:V41"/>
+    <mergeCell ref="U42:V42"/>
+    <mergeCell ref="U43:V43"/>
+    <mergeCell ref="U44:V44"/>
+    <mergeCell ref="U35:V35"/>
+    <mergeCell ref="U36:V36"/>
+    <mergeCell ref="U37:V37"/>
+    <mergeCell ref="U38:V38"/>
+    <mergeCell ref="U39:V39"/>
+    <mergeCell ref="U30:V30"/>
+    <mergeCell ref="U31:V31"/>
+    <mergeCell ref="U32:V32"/>
+    <mergeCell ref="U33:V33"/>
+    <mergeCell ref="U34:V34"/>
+    <mergeCell ref="U25:V25"/>
+    <mergeCell ref="U26:V26"/>
+    <mergeCell ref="U27:V27"/>
+    <mergeCell ref="U28:V28"/>
+    <mergeCell ref="U29:V29"/>
+    <mergeCell ref="U20:V20"/>
+    <mergeCell ref="U21:V21"/>
+    <mergeCell ref="U22:V22"/>
+    <mergeCell ref="U23:V23"/>
+    <mergeCell ref="U24:V24"/>
+    <mergeCell ref="U15:V15"/>
+    <mergeCell ref="U16:V16"/>
+    <mergeCell ref="U17:V17"/>
+    <mergeCell ref="U18:V18"/>
+    <mergeCell ref="U19:V19"/>
+    <mergeCell ref="U7:V7"/>
+    <mergeCell ref="U8:V8"/>
+    <mergeCell ref="U13:V13"/>
+    <mergeCell ref="U14:V14"/>
+    <mergeCell ref="F2:S2"/>
+    <mergeCell ref="X2:X5"/>
+    <mergeCell ref="F5:M5"/>
+    <mergeCell ref="T5:U5"/>
+    <mergeCell ref="F7:M7"/>
+    <mergeCell ref="X7:X8"/>
+    <mergeCell ref="F8:M8"/>
+    <mergeCell ref="S10:V10"/>
+    <mergeCell ref="S11:V11"/>
+    <mergeCell ref="U2:V3"/>
     <mergeCell ref="B10:B12"/>
     <mergeCell ref="C10:C12"/>
     <mergeCell ref="D10:D12"/>
@@ -7544,80 +7607,36 @@
     <mergeCell ref="AD10:AD12"/>
     <mergeCell ref="AE10:AE12"/>
     <mergeCell ref="U12:V12"/>
-    <mergeCell ref="U7:V7"/>
-    <mergeCell ref="U8:V8"/>
-    <mergeCell ref="U13:V13"/>
-    <mergeCell ref="U14:V14"/>
-    <mergeCell ref="F2:S2"/>
-    <mergeCell ref="X2:X5"/>
-    <mergeCell ref="F5:M5"/>
-    <mergeCell ref="T5:U5"/>
-    <mergeCell ref="F7:M7"/>
-    <mergeCell ref="X7:X8"/>
-    <mergeCell ref="F8:M8"/>
-    <mergeCell ref="U2:V2"/>
-    <mergeCell ref="S10:V10"/>
-    <mergeCell ref="S11:V11"/>
-    <mergeCell ref="U20:V20"/>
-    <mergeCell ref="U21:V21"/>
-    <mergeCell ref="U22:V22"/>
-    <mergeCell ref="U23:V23"/>
-    <mergeCell ref="U24:V24"/>
-    <mergeCell ref="U15:V15"/>
-    <mergeCell ref="U16:V16"/>
-    <mergeCell ref="U17:V17"/>
-    <mergeCell ref="U18:V18"/>
-    <mergeCell ref="U19:V19"/>
-    <mergeCell ref="U30:V30"/>
-    <mergeCell ref="U31:V31"/>
-    <mergeCell ref="U32:V32"/>
-    <mergeCell ref="U33:V33"/>
-    <mergeCell ref="U34:V34"/>
-    <mergeCell ref="U25:V25"/>
-    <mergeCell ref="U26:V26"/>
-    <mergeCell ref="U27:V27"/>
-    <mergeCell ref="U28:V28"/>
-    <mergeCell ref="U29:V29"/>
-    <mergeCell ref="U40:V40"/>
-    <mergeCell ref="U41:V41"/>
-    <mergeCell ref="U42:V42"/>
-    <mergeCell ref="U43:V43"/>
-    <mergeCell ref="U44:V44"/>
-    <mergeCell ref="U35:V35"/>
-    <mergeCell ref="U36:V36"/>
-    <mergeCell ref="U37:V37"/>
-    <mergeCell ref="U38:V38"/>
-    <mergeCell ref="U39:V39"/>
-    <mergeCell ref="U50:V50"/>
-    <mergeCell ref="U51:V51"/>
-    <mergeCell ref="U52:V52"/>
-    <mergeCell ref="U53:V53"/>
-    <mergeCell ref="U54:V54"/>
-    <mergeCell ref="U45:V45"/>
-    <mergeCell ref="U46:V46"/>
-    <mergeCell ref="U47:V47"/>
-    <mergeCell ref="U48:V48"/>
-    <mergeCell ref="U49:V49"/>
-    <mergeCell ref="U60:V60"/>
-    <mergeCell ref="U61:V61"/>
-    <mergeCell ref="U62:V62"/>
-    <mergeCell ref="U63:V63"/>
-    <mergeCell ref="U64:V64"/>
-    <mergeCell ref="U55:V55"/>
-    <mergeCell ref="U56:V56"/>
-    <mergeCell ref="U57:V57"/>
-    <mergeCell ref="U58:V58"/>
-    <mergeCell ref="U59:V59"/>
-    <mergeCell ref="U70:V70"/>
-    <mergeCell ref="U71:V71"/>
-    <mergeCell ref="U72:V72"/>
-    <mergeCell ref="U73:V73"/>
-    <mergeCell ref="S76:V76"/>
-    <mergeCell ref="U65:V65"/>
-    <mergeCell ref="U66:V66"/>
-    <mergeCell ref="U67:V67"/>
-    <mergeCell ref="U68:V68"/>
-    <mergeCell ref="U69:V69"/>
+    <mergeCell ref="B74:G74"/>
+    <mergeCell ref="F76:I76"/>
+    <mergeCell ref="M76:N76"/>
+    <mergeCell ref="O76:Q76"/>
+    <mergeCell ref="X78:X80"/>
+    <mergeCell ref="F80:I80"/>
+    <mergeCell ref="M80:N80"/>
+    <mergeCell ref="P80:Q80"/>
+    <mergeCell ref="F78:I78"/>
+    <mergeCell ref="M78:N78"/>
+    <mergeCell ref="P78:Q78"/>
+    <mergeCell ref="S78:V78"/>
+    <mergeCell ref="S80:V80"/>
+    <mergeCell ref="U82:V84"/>
+    <mergeCell ref="B90:I90"/>
+    <mergeCell ref="M90:Q90"/>
+    <mergeCell ref="R90:U90"/>
+    <mergeCell ref="B94:I94"/>
+    <mergeCell ref="B95:I95"/>
+    <mergeCell ref="R95:U95"/>
+    <mergeCell ref="Q82:R84"/>
+    <mergeCell ref="S82:S84"/>
+    <mergeCell ref="T82:T84"/>
+    <mergeCell ref="B89:I89"/>
+    <mergeCell ref="M89:Q89"/>
+    <mergeCell ref="B82:H84"/>
+    <mergeCell ref="I82:I84"/>
+    <mergeCell ref="M82:M84"/>
+    <mergeCell ref="N82:N84"/>
+    <mergeCell ref="O82:P84"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.19685039370078741" right="0" top="0" bottom="0" header="0" footer="0.19685039370078741"/>

--- a/GBDS APRIL FILES 2026/Guillermo DOS 2 - Neilven.xlsx
+++ b/GBDS APRIL FILES 2026/Guillermo DOS 2 - Neilven.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS APRIL FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F32DF6E-5230-4A77-9557-6A59849E00C5}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCF75D94-A7FD-499F-9F65-9CAD65867188}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2098,6 +2098,221 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="167" fontId="19" fillId="0" borderId="63" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="63" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="19" fillId="0" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="167" fontId="19" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="167" fontId="19" fillId="0" borderId="26" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="167" fontId="19" fillId="0" borderId="28" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="167" fontId="19" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="167" fontId="19" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="167" fontId="19" fillId="0" borderId="62" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="167" fontId="19" fillId="0" borderId="41" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="63" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="49" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="51" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="63" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="66" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="65" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="19" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="28" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="26" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="15" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="16" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="17" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="24" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="25" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="27" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="53" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="54" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="57" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="17" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="48" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="25" fillId="0" borderId="50" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="25" fillId="0" borderId="51" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="49" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="50" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="26" fillId="0" borderId="49" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="51" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="25" fillId="0" borderId="49" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="43" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="63" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
@@ -2225,221 +2440,6 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="55" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="48" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="25" fillId="0" borderId="50" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="25" fillId="0" borderId="51" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="49" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="50" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="26" fillId="0" borderId="49" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="51" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="25" fillId="0" borderId="49" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="63" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="43" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="19" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="28" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="26" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="15" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="16" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="17" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="24" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="25" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="27" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="53" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="54" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="57" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="17" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="63" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="49" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="51" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="167" fontId="19" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="167" fontId="19" fillId="0" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="63" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="19" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="167" fontId="19" fillId="0" borderId="41" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="167" fontId="19" fillId="0" borderId="28" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="167" fontId="19" fillId="0" borderId="62" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="167" fontId="19" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="167" fontId="19" fillId="0" borderId="63" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="167" fontId="19" fillId="0" borderId="26" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="65" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="66" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -2992,28 +2992,28 @@
       <c r="C2" s="93"/>
       <c r="D2" s="93"/>
       <c r="E2" s="93"/>
-      <c r="F2" s="285" t="s">
+      <c r="F2" s="207" t="s">
         <v>85</v>
       </c>
-      <c r="G2" s="285"/>
-      <c r="H2" s="285"/>
-      <c r="I2" s="285"/>
-      <c r="J2" s="285"/>
-      <c r="K2" s="285"/>
-      <c r="L2" s="285"/>
-      <c r="M2" s="285"/>
-      <c r="N2" s="285"/>
-      <c r="O2" s="285"/>
-      <c r="P2" s="285"/>
-      <c r="Q2" s="285"/>
-      <c r="R2" s="285"/>
-      <c r="S2" s="285"/>
+      <c r="G2" s="207"/>
+      <c r="H2" s="207"/>
+      <c r="I2" s="207"/>
+      <c r="J2" s="207"/>
+      <c r="K2" s="207"/>
+      <c r="L2" s="207"/>
+      <c r="M2" s="207"/>
+      <c r="N2" s="207"/>
+      <c r="O2" s="207"/>
+      <c r="P2" s="207"/>
+      <c r="Q2" s="207"/>
+      <c r="R2" s="207"/>
+      <c r="S2" s="207"/>
       <c r="T2" s="94" t="s">
         <v>1</v>
       </c>
-      <c r="U2" s="298"/>
-      <c r="V2" s="297"/>
-      <c r="X2" s="238" t="s">
+      <c r="U2" s="215"/>
+      <c r="V2" s="216"/>
+      <c r="X2" s="208" t="s">
         <v>2</v>
       </c>
       <c r="AB2" s="92">
@@ -3049,9 +3049,9 @@
       <c r="R3" s="193"/>
       <c r="S3" s="193"/>
       <c r="T3" s="94"/>
-      <c r="U3" s="298"/>
-      <c r="V3" s="297"/>
-      <c r="X3" s="239"/>
+      <c r="U3" s="215"/>
+      <c r="V3" s="216"/>
+      <c r="X3" s="209"/>
       <c r="AB3" s="92"/>
       <c r="AE3" s="92"/>
     </row>
@@ -3061,7 +3061,7 @@
       <c r="D4" s="93"/>
       <c r="E4" s="93"/>
       <c r="U4" s="186"/>
-      <c r="X4" s="239"/>
+      <c r="X4" s="209"/>
       <c r="AB4" s="92">
         <v>5.76</v>
       </c>
@@ -3082,21 +3082,21 @@
       <c r="C5" s="93"/>
       <c r="D5" s="93"/>
       <c r="E5" s="93"/>
-      <c r="F5" s="286"/>
-      <c r="G5" s="286"/>
-      <c r="H5" s="286"/>
-      <c r="I5" s="286"/>
-      <c r="J5" s="286"/>
-      <c r="K5" s="286"/>
-      <c r="L5" s="286"/>
-      <c r="M5" s="286"/>
+      <c r="F5" s="211"/>
+      <c r="G5" s="211"/>
+      <c r="H5" s="211"/>
+      <c r="I5" s="211"/>
+      <c r="J5" s="211"/>
+      <c r="K5" s="211"/>
+      <c r="L5" s="211"/>
+      <c r="M5" s="211"/>
       <c r="S5" s="91" t="s">
         <v>4</v>
       </c>
-      <c r="T5" s="287"/>
-      <c r="U5" s="287"/>
+      <c r="T5" s="212"/>
+      <c r="U5" s="212"/>
       <c r="V5" s="183"/>
-      <c r="X5" s="240"/>
+      <c r="X5" s="210"/>
       <c r="AB5" s="92">
         <v>5.07</v>
       </c>
@@ -3138,25 +3138,25 @@
       <c r="B7" s="91" t="s">
         <v>5</v>
       </c>
-      <c r="F7" s="288"/>
-      <c r="G7" s="288"/>
-      <c r="H7" s="288"/>
-      <c r="I7" s="288"/>
-      <c r="J7" s="288"/>
-      <c r="K7" s="288"/>
-      <c r="L7" s="288"/>
-      <c r="M7" s="288"/>
+      <c r="F7" s="213"/>
+      <c r="G7" s="213"/>
+      <c r="H7" s="213"/>
+      <c r="I7" s="213"/>
+      <c r="J7" s="213"/>
+      <c r="K7" s="213"/>
+      <c r="L7" s="213"/>
+      <c r="M7" s="213"/>
       <c r="S7" s="97" t="s">
         <v>6</v>
       </c>
       <c r="T7" s="163" t="s">
         <v>7</v>
       </c>
-      <c r="U7" s="280" t="s">
+      <c r="U7" s="204" t="s">
         <v>8</v>
       </c>
-      <c r="V7" s="280"/>
-      <c r="X7" s="238" t="s">
+      <c r="V7" s="204"/>
+      <c r="X7" s="208" t="s">
         <v>9</v>
       </c>
       <c r="AB7" s="92">
@@ -3179,14 +3179,14 @@
       <c r="C8" s="98"/>
       <c r="D8" s="98"/>
       <c r="E8" s="98"/>
-      <c r="F8" s="288"/>
-      <c r="G8" s="288"/>
-      <c r="H8" s="288"/>
-      <c r="I8" s="288"/>
-      <c r="J8" s="288"/>
-      <c r="K8" s="288"/>
-      <c r="L8" s="288"/>
-      <c r="M8" s="288"/>
+      <c r="F8" s="213"/>
+      <c r="G8" s="213"/>
+      <c r="H8" s="213"/>
+      <c r="I8" s="213"/>
+      <c r="J8" s="213"/>
+      <c r="K8" s="213"/>
+      <c r="L8" s="213"/>
+      <c r="M8" s="213"/>
       <c r="N8" s="99"/>
       <c r="O8" s="99"/>
       <c r="P8" s="99"/>
@@ -3195,9 +3195,9 @@
       <c r="T8" s="163" t="s">
         <v>11</v>
       </c>
-      <c r="U8" s="281"/>
-      <c r="V8" s="282"/>
-      <c r="X8" s="240"/>
+      <c r="U8" s="205"/>
+      <c r="V8" s="206"/>
+      <c r="X8" s="210"/>
       <c r="AB8" s="92">
         <v>5.25</v>
       </c>
@@ -3231,127 +3231,127 @@
       <c r="V9" s="95"/>
     </row>
     <row r="10" spans="2:35" s="100" customFormat="1" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="248" t="s">
+      <c r="B10" s="217" t="s">
         <v>12</v>
       </c>
-      <c r="C10" s="251" t="s">
+      <c r="C10" s="220" t="s">
         <v>13</v>
       </c>
-      <c r="D10" s="251" t="s">
+      <c r="D10" s="220" t="s">
         <v>14</v>
       </c>
-      <c r="E10" s="251" t="s">
+      <c r="E10" s="220" t="s">
         <v>15</v>
       </c>
-      <c r="F10" s="254" t="s">
+      <c r="F10" s="223" t="s">
         <v>16</v>
       </c>
-      <c r="G10" s="255"/>
-      <c r="H10" s="255"/>
-      <c r="I10" s="255"/>
-      <c r="J10" s="255"/>
-      <c r="K10" s="255"/>
-      <c r="L10" s="255"/>
-      <c r="M10" s="255"/>
-      <c r="N10" s="255"/>
-      <c r="O10" s="255"/>
-      <c r="P10" s="255"/>
-      <c r="Q10" s="256"/>
-      <c r="S10" s="289" t="s">
+      <c r="G10" s="224"/>
+      <c r="H10" s="224"/>
+      <c r="I10" s="224"/>
+      <c r="J10" s="224"/>
+      <c r="K10" s="224"/>
+      <c r="L10" s="224"/>
+      <c r="M10" s="224"/>
+      <c r="N10" s="224"/>
+      <c r="O10" s="224"/>
+      <c r="P10" s="224"/>
+      <c r="Q10" s="225"/>
+      <c r="S10" s="214" t="s">
         <v>17</v>
       </c>
-      <c r="T10" s="289"/>
-      <c r="U10" s="289"/>
-      <c r="V10" s="289"/>
-      <c r="Y10" s="267" t="s">
+      <c r="T10" s="214"/>
+      <c r="U10" s="214"/>
+      <c r="V10" s="214"/>
+      <c r="Y10" s="236" t="s">
         <v>18</v>
       </c>
-      <c r="Z10" s="270" t="s">
+      <c r="Z10" s="239" t="s">
         <v>19</v>
       </c>
       <c r="AA10" s="101"/>
-      <c r="AB10" s="257" t="s">
+      <c r="AB10" s="226" t="s">
         <v>20</v>
       </c>
-      <c r="AC10" s="273" t="s">
+      <c r="AC10" s="242" t="s">
         <v>21</v>
       </c>
-      <c r="AD10" s="276" t="s">
+      <c r="AD10" s="245" t="s">
         <v>84</v>
       </c>
-      <c r="AE10" s="257" t="s">
+      <c r="AE10" s="226" t="s">
         <v>22</v>
       </c>
-      <c r="AG10" s="257" t="s">
+      <c r="AG10" s="226" t="s">
         <v>23</v>
       </c>
       <c r="AH10" s="101"/>
-      <c r="AI10" s="257" t="s">
+      <c r="AI10" s="226" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="11" spans="2:35" s="100" customFormat="1" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="249"/>
-      <c r="C11" s="252"/>
-      <c r="D11" s="252"/>
-      <c r="E11" s="252"/>
-      <c r="F11" s="261" t="s">
+      <c r="B11" s="218"/>
+      <c r="C11" s="221"/>
+      <c r="D11" s="221"/>
+      <c r="E11" s="221"/>
+      <c r="F11" s="230" t="s">
         <v>25</v>
       </c>
-      <c r="G11" s="261" t="s">
+      <c r="G11" s="230" t="s">
         <v>26</v>
       </c>
-      <c r="H11" s="261" t="s">
+      <c r="H11" s="230" t="s">
         <v>27</v>
       </c>
-      <c r="I11" s="262" t="s">
+      <c r="I11" s="231" t="s">
         <v>28</v>
       </c>
-      <c r="J11" s="262" t="s">
+      <c r="J11" s="231" t="s">
         <v>29</v>
       </c>
-      <c r="K11" s="262" t="s">
+      <c r="K11" s="231" t="s">
         <v>30</v>
       </c>
-      <c r="L11" s="262" t="s">
+      <c r="L11" s="231" t="s">
         <v>31</v>
       </c>
-      <c r="M11" s="264" t="s">
+      <c r="M11" s="233" t="s">
         <v>32</v>
       </c>
-      <c r="N11" s="265"/>
-      <c r="O11" s="265"/>
-      <c r="P11" s="265"/>
-      <c r="Q11" s="266"/>
-      <c r="S11" s="289" t="s">
+      <c r="N11" s="234"/>
+      <c r="O11" s="234"/>
+      <c r="P11" s="234"/>
+      <c r="Q11" s="235"/>
+      <c r="S11" s="214" t="s">
         <v>33</v>
       </c>
-      <c r="T11" s="289"/>
-      <c r="U11" s="289"/>
-      <c r="V11" s="289"/>
-      <c r="Y11" s="268"/>
-      <c r="Z11" s="271"/>
+      <c r="T11" s="214"/>
+      <c r="U11" s="214"/>
+      <c r="V11" s="214"/>
+      <c r="Y11" s="237"/>
+      <c r="Z11" s="240"/>
       <c r="AA11" s="101"/>
-      <c r="AB11" s="258"/>
-      <c r="AC11" s="274"/>
-      <c r="AD11" s="277"/>
-      <c r="AE11" s="258"/>
-      <c r="AG11" s="258"/>
+      <c r="AB11" s="227"/>
+      <c r="AC11" s="243"/>
+      <c r="AD11" s="246"/>
+      <c r="AE11" s="227"/>
+      <c r="AG11" s="227"/>
       <c r="AH11" s="101"/>
-      <c r="AI11" s="258"/>
+      <c r="AI11" s="227"/>
     </row>
     <row r="12" spans="2:35" s="102" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="250"/>
-      <c r="C12" s="253"/>
-      <c r="D12" s="253"/>
-      <c r="E12" s="253"/>
-      <c r="F12" s="253"/>
-      <c r="G12" s="253"/>
-      <c r="H12" s="253"/>
-      <c r="I12" s="263"/>
-      <c r="J12" s="263"/>
-      <c r="K12" s="263"/>
-      <c r="L12" s="263"/>
+      <c r="B12" s="219"/>
+      <c r="C12" s="222"/>
+      <c r="D12" s="222"/>
+      <c r="E12" s="222"/>
+      <c r="F12" s="222"/>
+      <c r="G12" s="222"/>
+      <c r="H12" s="222"/>
+      <c r="I12" s="232"/>
+      <c r="J12" s="232"/>
+      <c r="K12" s="232"/>
+      <c r="L12" s="232"/>
       <c r="M12" s="4" t="s">
         <v>34</v>
       </c>
@@ -3373,20 +3373,20 @@
       <c r="T12" s="188" t="s">
         <v>35</v>
       </c>
-      <c r="U12" s="279" t="s">
+      <c r="U12" s="248" t="s">
         <v>36</v>
       </c>
-      <c r="V12" s="279"/>
-      <c r="Y12" s="269"/>
-      <c r="Z12" s="272"/>
+      <c r="V12" s="248"/>
+      <c r="Y12" s="238"/>
+      <c r="Z12" s="241"/>
       <c r="AA12" s="101"/>
-      <c r="AB12" s="260"/>
-      <c r="AC12" s="275"/>
-      <c r="AD12" s="278"/>
-      <c r="AE12" s="260"/>
-      <c r="AG12" s="259"/>
+      <c r="AB12" s="229"/>
+      <c r="AC12" s="244"/>
+      <c r="AD12" s="247"/>
+      <c r="AE12" s="229"/>
+      <c r="AG12" s="228"/>
       <c r="AH12" s="101"/>
-      <c r="AI12" s="260"/>
+      <c r="AI12" s="229"/>
     </row>
     <row r="13" spans="2:35" s="102" customFormat="1" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="103" t="s">
@@ -3416,8 +3416,8 @@
       <c r="Q13" s="13"/>
       <c r="S13" s="14"/>
       <c r="T13" s="189"/>
-      <c r="U13" s="283"/>
-      <c r="V13" s="283"/>
+      <c r="U13" s="201"/>
+      <c r="V13" s="201"/>
       <c r="Y13" s="105">
         <f>F13*C13</f>
         <v>0</v>
@@ -3480,8 +3480,8 @@
       <c r="Q14" s="22"/>
       <c r="S14" s="23"/>
       <c r="T14" s="23"/>
-      <c r="U14" s="284"/>
-      <c r="V14" s="284"/>
+      <c r="U14" s="196"/>
+      <c r="V14" s="196"/>
       <c r="Y14" s="115">
         <f t="shared" ref="Y14:Y71" si="3">F14*C14</f>
         <v>0</v>
@@ -3544,8 +3544,8 @@
       <c r="Q15" s="22"/>
       <c r="S15" s="23"/>
       <c r="T15" s="23"/>
-      <c r="U15" s="284"/>
-      <c r="V15" s="284"/>
+      <c r="U15" s="196"/>
+      <c r="V15" s="196"/>
       <c r="Y15" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -3608,8 +3608,8 @@
       <c r="Q16" s="22"/>
       <c r="S16" s="23"/>
       <c r="T16" s="23"/>
-      <c r="U16" s="290"/>
-      <c r="V16" s="290"/>
+      <c r="U16" s="197"/>
+      <c r="V16" s="197"/>
       <c r="Y16" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -3672,8 +3672,8 @@
       <c r="Q17" s="22"/>
       <c r="S17" s="23"/>
       <c r="T17" s="26"/>
-      <c r="U17" s="292"/>
-      <c r="V17" s="292"/>
+      <c r="U17" s="199"/>
+      <c r="V17" s="199"/>
       <c r="Y17" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -3736,8 +3736,8 @@
       <c r="Q18" s="22"/>
       <c r="S18" s="23"/>
       <c r="T18" s="26"/>
-      <c r="U18" s="292"/>
-      <c r="V18" s="292"/>
+      <c r="U18" s="199"/>
+      <c r="V18" s="199"/>
       <c r="Y18" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -3800,8 +3800,8 @@
       <c r="Q19" s="33"/>
       <c r="S19" s="34"/>
       <c r="T19" s="35"/>
-      <c r="U19" s="291"/>
-      <c r="V19" s="291"/>
+      <c r="U19" s="203"/>
+      <c r="V19" s="203"/>
       <c r="Y19" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -3864,8 +3864,8 @@
       <c r="Q20" s="22"/>
       <c r="S20" s="23"/>
       <c r="T20" s="26"/>
-      <c r="U20" s="290"/>
-      <c r="V20" s="290"/>
+      <c r="U20" s="197"/>
+      <c r="V20" s="197"/>
       <c r="Y20" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -3928,8 +3928,8 @@
       <c r="Q21" s="33"/>
       <c r="S21" s="34"/>
       <c r="T21" s="35"/>
-      <c r="U21" s="291"/>
-      <c r="V21" s="291"/>
+      <c r="U21" s="203"/>
+      <c r="V21" s="203"/>
       <c r="Y21" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -3992,8 +3992,8 @@
       <c r="Q22" s="42"/>
       <c r="S22" s="43"/>
       <c r="T22" s="44"/>
-      <c r="U22" s="290"/>
-      <c r="V22" s="290"/>
+      <c r="U22" s="197"/>
+      <c r="V22" s="197"/>
       <c r="Y22" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -4056,8 +4056,8 @@
       <c r="Q23" s="22"/>
       <c r="S23" s="23"/>
       <c r="T23" s="26"/>
-      <c r="U23" s="292"/>
-      <c r="V23" s="292"/>
+      <c r="U23" s="199"/>
+      <c r="V23" s="199"/>
       <c r="Y23" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -4120,8 +4120,8 @@
       <c r="Q24" s="22"/>
       <c r="S24" s="23"/>
       <c r="T24" s="26"/>
-      <c r="U24" s="284"/>
-      <c r="V24" s="284"/>
+      <c r="U24" s="196"/>
+      <c r="V24" s="196"/>
       <c r="Y24" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -4184,8 +4184,8 @@
       <c r="Q25" s="33"/>
       <c r="S25" s="34"/>
       <c r="T25" s="35"/>
-      <c r="U25" s="292"/>
-      <c r="V25" s="292"/>
+      <c r="U25" s="199"/>
+      <c r="V25" s="199"/>
       <c r="Y25" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -4248,8 +4248,8 @@
       <c r="Q26" s="42"/>
       <c r="S26" s="43"/>
       <c r="T26" s="44"/>
-      <c r="U26" s="293"/>
-      <c r="V26" s="293"/>
+      <c r="U26" s="202"/>
+      <c r="V26" s="202"/>
       <c r="Y26" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -4312,8 +4312,8 @@
       <c r="Q27" s="33"/>
       <c r="S27" s="34"/>
       <c r="T27" s="35"/>
-      <c r="U27" s="290"/>
-      <c r="V27" s="290"/>
+      <c r="U27" s="197"/>
+      <c r="V27" s="197"/>
       <c r="Y27" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -4376,8 +4376,8 @@
       <c r="Q28" s="42"/>
       <c r="S28" s="43"/>
       <c r="T28" s="44"/>
-      <c r="U28" s="293"/>
-      <c r="V28" s="293"/>
+      <c r="U28" s="202"/>
+      <c r="V28" s="202"/>
       <c r="Y28" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -4440,8 +4440,8 @@
       <c r="Q29" s="22"/>
       <c r="S29" s="23"/>
       <c r="T29" s="26"/>
-      <c r="U29" s="290"/>
-      <c r="V29" s="290"/>
+      <c r="U29" s="197"/>
+      <c r="V29" s="197"/>
       <c r="Y29" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -4502,8 +4502,8 @@
       <c r="Q30" s="22"/>
       <c r="S30" s="23"/>
       <c r="T30" s="26"/>
-      <c r="U30" s="284"/>
-      <c r="V30" s="284"/>
+      <c r="U30" s="196"/>
+      <c r="V30" s="196"/>
       <c r="Y30" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -4564,8 +4564,8 @@
       <c r="Q31" s="22"/>
       <c r="S31" s="26"/>
       <c r="T31" s="26"/>
-      <c r="U31" s="292"/>
-      <c r="V31" s="292"/>
+      <c r="U31" s="199"/>
+      <c r="V31" s="199"/>
       <c r="Y31" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -4626,8 +4626,8 @@
       <c r="Q32" s="22"/>
       <c r="S32" s="26"/>
       <c r="T32" s="26"/>
-      <c r="U32" s="284"/>
-      <c r="V32" s="284"/>
+      <c r="U32" s="196"/>
+      <c r="V32" s="196"/>
       <c r="Y32" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -4683,8 +4683,8 @@
       <c r="Q33" s="22"/>
       <c r="S33" s="26"/>
       <c r="T33" s="26"/>
-      <c r="U33" s="284"/>
-      <c r="V33" s="284"/>
+      <c r="U33" s="196"/>
+      <c r="V33" s="196"/>
       <c r="Y33" s="115"/>
       <c r="Z33" s="116"/>
       <c r="AA33" s="107"/>
@@ -4723,8 +4723,8 @@
       <c r="Q34" s="22"/>
       <c r="S34" s="26"/>
       <c r="T34" s="26"/>
-      <c r="U34" s="284"/>
-      <c r="V34" s="284"/>
+      <c r="U34" s="196"/>
+      <c r="V34" s="196"/>
       <c r="Y34" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -4785,8 +4785,8 @@
       <c r="Q35" s="22"/>
       <c r="S35" s="26"/>
       <c r="T35" s="26"/>
-      <c r="U35" s="284"/>
-      <c r="V35" s="284"/>
+      <c r="U35" s="196"/>
+      <c r="V35" s="196"/>
       <c r="Y35" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -4847,8 +4847,8 @@
       <c r="Q36" s="33"/>
       <c r="S36" s="35"/>
       <c r="T36" s="35"/>
-      <c r="U36" s="290"/>
-      <c r="V36" s="290"/>
+      <c r="U36" s="197"/>
+      <c r="V36" s="197"/>
       <c r="Y36" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -4909,8 +4909,8 @@
       <c r="Q37" s="42"/>
       <c r="S37" s="44"/>
       <c r="T37" s="44"/>
-      <c r="U37" s="293"/>
-      <c r="V37" s="293"/>
+      <c r="U37" s="202"/>
+      <c r="V37" s="202"/>
       <c r="Y37" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -4971,8 +4971,8 @@
       <c r="Q38" s="22"/>
       <c r="S38" s="26"/>
       <c r="T38" s="26"/>
-      <c r="U38" s="290"/>
-      <c r="V38" s="290"/>
+      <c r="U38" s="197"/>
+      <c r="V38" s="197"/>
       <c r="Y38" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -5033,8 +5033,8 @@
       <c r="Q39" s="33"/>
       <c r="S39" s="35"/>
       <c r="T39" s="35"/>
-      <c r="U39" s="291"/>
-      <c r="V39" s="291"/>
+      <c r="U39" s="203"/>
+      <c r="V39" s="203"/>
       <c r="Y39" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -5095,8 +5095,8 @@
       <c r="Q40" s="42"/>
       <c r="S40" s="44"/>
       <c r="T40" s="44"/>
-      <c r="U40" s="290"/>
-      <c r="V40" s="290"/>
+      <c r="U40" s="197"/>
+      <c r="V40" s="197"/>
       <c r="Y40" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -5157,8 +5157,8 @@
       <c r="Q41" s="22"/>
       <c r="S41" s="26"/>
       <c r="T41" s="26"/>
-      <c r="U41" s="292"/>
-      <c r="V41" s="292"/>
+      <c r="U41" s="199"/>
+      <c r="V41" s="199"/>
       <c r="Y41" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -5219,8 +5219,8 @@
       <c r="Q42" s="22"/>
       <c r="S42" s="26"/>
       <c r="T42" s="26"/>
-      <c r="U42" s="292"/>
-      <c r="V42" s="292"/>
+      <c r="U42" s="199"/>
+      <c r="V42" s="199"/>
       <c r="Y42" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -5276,8 +5276,8 @@
       <c r="Q43" s="33"/>
       <c r="S43" s="35"/>
       <c r="T43" s="35"/>
-      <c r="U43" s="291"/>
-      <c r="V43" s="291"/>
+      <c r="U43" s="203"/>
+      <c r="V43" s="203"/>
       <c r="Y43" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -5331,8 +5331,8 @@
       <c r="Q44" s="22"/>
       <c r="S44" s="23"/>
       <c r="T44" s="26"/>
-      <c r="U44" s="294"/>
-      <c r="V44" s="294"/>
+      <c r="U44" s="200"/>
+      <c r="V44" s="200"/>
       <c r="Y44" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -5383,8 +5383,8 @@
       <c r="Q45" s="22"/>
       <c r="S45" s="23"/>
       <c r="T45" s="26"/>
-      <c r="U45" s="295"/>
-      <c r="V45" s="295"/>
+      <c r="U45" s="194"/>
+      <c r="V45" s="194"/>
       <c r="Y45" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -5435,8 +5435,8 @@
       <c r="Q46" s="33"/>
       <c r="S46" s="34"/>
       <c r="T46" s="35"/>
-      <c r="U46" s="283"/>
-      <c r="V46" s="283"/>
+      <c r="U46" s="201"/>
+      <c r="V46" s="201"/>
       <c r="Y46" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -5484,8 +5484,8 @@
       <c r="Q47" s="174"/>
       <c r="S47" s="171"/>
       <c r="T47" s="172"/>
-      <c r="U47" s="293"/>
-      <c r="V47" s="293"/>
+      <c r="U47" s="202"/>
+      <c r="V47" s="202"/>
       <c r="Y47" s="115"/>
       <c r="Z47" s="116"/>
       <c r="AA47" s="107"/>
@@ -5526,8 +5526,8 @@
       <c r="Q48" s="22"/>
       <c r="S48" s="23"/>
       <c r="T48" s="26"/>
-      <c r="U48" s="284"/>
-      <c r="V48" s="284"/>
+      <c r="U48" s="196"/>
+      <c r="V48" s="196"/>
       <c r="Y48" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -5588,8 +5588,8 @@
       <c r="Q49" s="22"/>
       <c r="S49" s="26"/>
       <c r="T49" s="26"/>
-      <c r="U49" s="284"/>
-      <c r="V49" s="284"/>
+      <c r="U49" s="196"/>
+      <c r="V49" s="196"/>
       <c r="Y49" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -5652,8 +5652,8 @@
       <c r="Q50" s="22"/>
       <c r="S50" s="23"/>
       <c r="T50" s="26"/>
-      <c r="U50" s="284"/>
-      <c r="V50" s="284"/>
+      <c r="U50" s="196"/>
+      <c r="V50" s="196"/>
       <c r="Y50" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -5716,8 +5716,8 @@
       <c r="Q51" s="57"/>
       <c r="S51" s="58"/>
       <c r="T51" s="58"/>
-      <c r="U51" s="294"/>
-      <c r="V51" s="294"/>
+      <c r="U51" s="200"/>
+      <c r="V51" s="200"/>
       <c r="Y51" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -5776,8 +5776,8 @@
       <c r="Q52" s="42"/>
       <c r="S52" s="44"/>
       <c r="T52" s="44"/>
-      <c r="U52" s="295"/>
-      <c r="V52" s="295"/>
+      <c r="U52" s="194"/>
+      <c r="V52" s="194"/>
       <c r="Y52" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -5836,8 +5836,8 @@
       <c r="Q53" s="22"/>
       <c r="S53" s="23"/>
       <c r="T53" s="23"/>
-      <c r="U53" s="283"/>
-      <c r="V53" s="283"/>
+      <c r="U53" s="201"/>
+      <c r="V53" s="201"/>
       <c r="Y53" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -5890,8 +5890,8 @@
       <c r="Q54" s="22"/>
       <c r="S54" s="23"/>
       <c r="T54" s="23"/>
-      <c r="U54" s="292"/>
-      <c r="V54" s="292"/>
+      <c r="U54" s="199"/>
+      <c r="V54" s="199"/>
       <c r="Y54" s="115"/>
       <c r="Z54" s="116"/>
       <c r="AA54" s="107"/>
@@ -5925,8 +5925,8 @@
       <c r="Q55" s="22"/>
       <c r="S55" s="23"/>
       <c r="T55" s="23"/>
-      <c r="U55" s="292"/>
-      <c r="V55" s="292"/>
+      <c r="U55" s="199"/>
+      <c r="V55" s="199"/>
       <c r="Y55" s="115"/>
       <c r="Z55" s="116"/>
       <c r="AA55" s="107"/>
@@ -5960,8 +5960,8 @@
       <c r="Q56" s="22"/>
       <c r="S56" s="23"/>
       <c r="T56" s="23"/>
-      <c r="U56" s="284"/>
-      <c r="V56" s="284"/>
+      <c r="U56" s="196"/>
+      <c r="V56" s="196"/>
       <c r="Y56" s="115"/>
       <c r="Z56" s="116"/>
       <c r="AA56" s="107"/>
@@ -6002,8 +6002,8 @@
       <c r="Q57" s="22"/>
       <c r="S57" s="23"/>
       <c r="T57" s="26"/>
-      <c r="U57" s="290"/>
-      <c r="V57" s="290"/>
+      <c r="U57" s="197"/>
+      <c r="V57" s="197"/>
       <c r="Y57" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -6056,8 +6056,8 @@
       <c r="Q58" s="22"/>
       <c r="S58" s="23"/>
       <c r="T58" s="26"/>
-      <c r="U58" s="292"/>
-      <c r="V58" s="292"/>
+      <c r="U58" s="199"/>
+      <c r="V58" s="199"/>
       <c r="Y58" s="115"/>
       <c r="Z58" s="116"/>
       <c r="AA58" s="107"/>
@@ -6091,8 +6091,8 @@
       <c r="Q59" s="22"/>
       <c r="S59" s="23"/>
       <c r="T59" s="26"/>
-      <c r="U59" s="292"/>
-      <c r="V59" s="292"/>
+      <c r="U59" s="199"/>
+      <c r="V59" s="199"/>
       <c r="Y59" s="115"/>
       <c r="Z59" s="116"/>
       <c r="AA59" s="107"/>
@@ -6126,8 +6126,8 @@
       <c r="Q60" s="22"/>
       <c r="S60" s="23"/>
       <c r="T60" s="26"/>
-      <c r="U60" s="284"/>
-      <c r="V60" s="284"/>
+      <c r="U60" s="196"/>
+      <c r="V60" s="196"/>
       <c r="Y60" s="115"/>
       <c r="Z60" s="116"/>
       <c r="AA60" s="107"/>
@@ -6159,8 +6159,8 @@
       <c r="Q61" s="22"/>
       <c r="S61" s="23"/>
       <c r="T61" s="26"/>
-      <c r="U61" s="290"/>
-      <c r="V61" s="290"/>
+      <c r="U61" s="197"/>
+      <c r="V61" s="197"/>
       <c r="Y61" s="115"/>
       <c r="Z61" s="116"/>
       <c r="AA61" s="107"/>
@@ -6199,8 +6199,8 @@
       <c r="Q62" s="22"/>
       <c r="S62" s="180"/>
       <c r="T62" s="59"/>
-      <c r="U62" s="296"/>
-      <c r="V62" s="296"/>
+      <c r="U62" s="198"/>
+      <c r="V62" s="198"/>
       <c r="Y62" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -6260,8 +6260,8 @@
       <c r="Q63" s="22"/>
       <c r="S63" s="43"/>
       <c r="T63" s="44"/>
-      <c r="U63" s="295"/>
-      <c r="V63" s="295"/>
+      <c r="U63" s="194"/>
+      <c r="V63" s="194"/>
       <c r="Y63" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -6320,8 +6320,8 @@
       <c r="Q64" s="33"/>
       <c r="S64" s="34"/>
       <c r="T64" s="35"/>
-      <c r="U64" s="295"/>
-      <c r="V64" s="295"/>
+      <c r="U64" s="194"/>
+      <c r="V64" s="194"/>
       <c r="Y64" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -6379,8 +6379,8 @@
       <c r="Q65" s="42"/>
       <c r="S65" s="44"/>
       <c r="T65" s="44"/>
-      <c r="U65" s="295"/>
-      <c r="V65" s="295"/>
+      <c r="U65" s="194"/>
+      <c r="V65" s="194"/>
       <c r="Y65" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -6441,8 +6441,8 @@
       <c r="Q66" s="22"/>
       <c r="S66" s="26"/>
       <c r="T66" s="26"/>
-      <c r="U66" s="295"/>
-      <c r="V66" s="295"/>
+      <c r="U66" s="194"/>
+      <c r="V66" s="194"/>
       <c r="Y66" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -6503,8 +6503,8 @@
       <c r="Q67" s="22"/>
       <c r="S67" s="26"/>
       <c r="T67" s="26"/>
-      <c r="U67" s="295"/>
-      <c r="V67" s="295"/>
+      <c r="U67" s="194"/>
+      <c r="V67" s="194"/>
       <c r="Y67" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -6565,8 +6565,8 @@
       <c r="Q68" s="22"/>
       <c r="S68" s="26"/>
       <c r="T68" s="26"/>
-      <c r="U68" s="295"/>
-      <c r="V68" s="295"/>
+      <c r="U68" s="194"/>
+      <c r="V68" s="194"/>
       <c r="Y68" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -6627,8 +6627,8 @@
       <c r="Q69" s="22"/>
       <c r="S69" s="26"/>
       <c r="T69" s="26"/>
-      <c r="U69" s="295"/>
-      <c r="V69" s="295"/>
+      <c r="U69" s="194"/>
+      <c r="V69" s="194"/>
       <c r="Y69" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -6689,8 +6689,8 @@
       <c r="Q70" s="22"/>
       <c r="S70" s="26"/>
       <c r="T70" s="26"/>
-      <c r="U70" s="295"/>
-      <c r="V70" s="295"/>
+      <c r="U70" s="194"/>
+      <c r="V70" s="194"/>
       <c r="Y70" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -6751,8 +6751,8 @@
       <c r="Q71" s="57"/>
       <c r="S71" s="58"/>
       <c r="T71" s="58"/>
-      <c r="U71" s="295"/>
-      <c r="V71" s="295"/>
+      <c r="U71" s="194"/>
+      <c r="V71" s="194"/>
       <c r="Y71" s="131">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -6829,8 +6829,8 @@
       </c>
       <c r="S72" s="64"/>
       <c r="T72" s="64"/>
-      <c r="U72" s="295"/>
-      <c r="V72" s="295"/>
+      <c r="U72" s="194"/>
+      <c r="V72" s="194"/>
       <c r="AB72" s="102">
         <v>0.61</v>
       </c>
@@ -6877,21 +6877,21 @@
       </c>
       <c r="S73" s="70"/>
       <c r="T73" s="70"/>
-      <c r="U73" s="295"/>
-      <c r="V73" s="295"/>
+      <c r="U73" s="194"/>
+      <c r="V73" s="194"/>
       <c r="AB73" s="102">
         <v>0.61</v>
       </c>
     </row>
     <row r="74" spans="2:35" s="102" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B74" s="233" t="s">
+      <c r="B74" s="249" t="s">
         <v>55</v>
       </c>
-      <c r="C74" s="233"/>
-      <c r="D74" s="233"/>
-      <c r="E74" s="233"/>
-      <c r="F74" s="233"/>
-      <c r="G74" s="233"/>
+      <c r="C74" s="249"/>
+      <c r="D74" s="249"/>
+      <c r="E74" s="249"/>
+      <c r="F74" s="249"/>
+      <c r="G74" s="249"/>
       <c r="H74" s="72" t="str">
         <f>ROUND(((F13+F28+F52+F53+F57+F62+F63+F64)/72+(F14+F17+F18)/108+(F15+SUM(F19:F27)+F29+F30+F48+F50+F42)/63+F16/96+SUM(F31:F41)/100+SUM(F44:F46)/24+SUM(F65:F71)/100+(F51+F43+F49)/100),1)&amp;" pallets"</f>
         <v>0 pallets</v>
@@ -6967,27 +6967,27 @@
       <c r="C76" s="142"/>
       <c r="D76" s="142"/>
       <c r="E76" s="142"/>
-      <c r="F76" s="234"/>
-      <c r="G76" s="234"/>
-      <c r="H76" s="234"/>
-      <c r="I76" s="235"/>
+      <c r="F76" s="250"/>
+      <c r="G76" s="250"/>
+      <c r="H76" s="250"/>
+      <c r="I76" s="251"/>
       <c r="J76" s="77"/>
       <c r="K76" s="77"/>
       <c r="L76" s="77"/>
-      <c r="M76" s="236" t="s">
+      <c r="M76" s="252" t="s">
         <v>57</v>
       </c>
-      <c r="N76" s="237"/>
-      <c r="O76" s="234"/>
-      <c r="P76" s="234"/>
-      <c r="Q76" s="235"/>
+      <c r="N76" s="253"/>
+      <c r="O76" s="250"/>
+      <c r="P76" s="250"/>
+      <c r="Q76" s="251"/>
       <c r="R76" s="139"/>
-      <c r="S76" s="245" t="s">
+      <c r="S76" s="195" t="s">
         <v>58</v>
       </c>
-      <c r="T76" s="245"/>
-      <c r="U76" s="245"/>
-      <c r="V76" s="245"/>
+      <c r="T76" s="195"/>
+      <c r="U76" s="195"/>
+      <c r="V76" s="195"/>
       <c r="W76" s="78"/>
       <c r="X76" s="78"/>
       <c r="Y76" s="78"/>
@@ -7042,31 +7042,31 @@
       <c r="C78" s="142"/>
       <c r="D78" s="142"/>
       <c r="E78" s="142"/>
-      <c r="F78" s="234"/>
-      <c r="G78" s="234"/>
-      <c r="H78" s="234"/>
-      <c r="I78" s="235"/>
+      <c r="F78" s="250"/>
+      <c r="G78" s="250"/>
+      <c r="H78" s="250"/>
+      <c r="I78" s="251"/>
       <c r="J78" s="80"/>
       <c r="K78" s="80"/>
       <c r="L78" s="80"/>
-      <c r="M78" s="244" t="s">
+      <c r="M78" s="257" t="s">
         <v>60</v>
       </c>
-      <c r="N78" s="244"/>
+      <c r="N78" s="257"/>
       <c r="O78" s="82" t="s">
         <v>61</v>
       </c>
-      <c r="P78" s="243"/>
-      <c r="Q78" s="235"/>
+      <c r="P78" s="256"/>
+      <c r="Q78" s="251"/>
       <c r="R78" s="139"/>
-      <c r="S78" s="245" t="s">
+      <c r="S78" s="195" t="s">
         <v>62</v>
       </c>
-      <c r="T78" s="245"/>
-      <c r="U78" s="245"/>
-      <c r="V78" s="245"/>
+      <c r="T78" s="195"/>
+      <c r="U78" s="195"/>
+      <c r="V78" s="195"/>
       <c r="W78" s="78"/>
-      <c r="X78" s="238" t="s">
+      <c r="X78" s="208" t="s">
         <v>63</v>
       </c>
       <c r="Y78" s="78"/>
@@ -7101,7 +7101,7 @@
       <c r="U79" s="81"/>
       <c r="V79" s="81"/>
       <c r="W79" s="78"/>
-      <c r="X79" s="239"/>
+      <c r="X79" s="209"/>
       <c r="Y79" s="78"/>
       <c r="Z79" s="78"/>
       <c r="AA79" s="78"/>
@@ -7121,35 +7121,35 @@
       <c r="C80" s="142"/>
       <c r="D80" s="142"/>
       <c r="E80" s="142"/>
-      <c r="F80" s="234" t="str">
+      <c r="F80" s="250" t="str">
         <f>IF(U7&gt;0,"",F76-T80)</f>
         <v/>
       </c>
-      <c r="G80" s="234"/>
-      <c r="H80" s="234"/>
-      <c r="I80" s="235"/>
+      <c r="G80" s="250"/>
+      <c r="H80" s="250"/>
+      <c r="I80" s="251"/>
       <c r="J80" s="80"/>
       <c r="K80" s="80"/>
       <c r="L80" s="80"/>
-      <c r="M80" s="241" t="str">
+      <c r="M80" s="254" t="str">
         <f>IF(U7&gt;0,"",T5+30)</f>
         <v/>
       </c>
-      <c r="N80" s="242"/>
+      <c r="N80" s="255"/>
       <c r="O80" s="82" t="s">
         <v>65</v>
       </c>
-      <c r="P80" s="243"/>
-      <c r="Q80" s="235"/>
+      <c r="P80" s="256"/>
+      <c r="Q80" s="251"/>
       <c r="R80" s="139"/>
-      <c r="S80" s="246" t="s">
+      <c r="S80" s="258" t="s">
         <v>66</v>
       </c>
-      <c r="T80" s="247"/>
-      <c r="U80" s="247"/>
-      <c r="V80" s="247"/>
+      <c r="T80" s="259"/>
+      <c r="U80" s="259"/>
+      <c r="V80" s="259"/>
       <c r="W80" s="78"/>
-      <c r="X80" s="240"/>
+      <c r="X80" s="210"/>
       <c r="Y80" s="78"/>
       <c r="Z80" s="78"/>
       <c r="AA80" s="78"/>
@@ -7199,83 +7199,83 @@
       <c r="AI81" s="78"/>
     </row>
     <row r="82" spans="2:35" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B82" s="213" t="s">
+      <c r="B82" s="279" t="s">
         <v>67</v>
       </c>
-      <c r="C82" s="214"/>
-      <c r="D82" s="214"/>
-      <c r="E82" s="214"/>
-      <c r="F82" s="214"/>
-      <c r="G82" s="214"/>
-      <c r="H82" s="215"/>
-      <c r="I82" s="222" t="s">
+      <c r="C82" s="280"/>
+      <c r="D82" s="280"/>
+      <c r="E82" s="280"/>
+      <c r="F82" s="280"/>
+      <c r="G82" s="280"/>
+      <c r="H82" s="281"/>
+      <c r="I82" s="288" t="s">
         <v>68</v>
       </c>
       <c r="J82" s="148"/>
       <c r="K82" s="148"/>
       <c r="L82" s="148"/>
-      <c r="M82" s="224"/>
-      <c r="N82" s="227" t="s">
+      <c r="M82" s="290"/>
+      <c r="N82" s="293" t="s">
         <v>69</v>
       </c>
-      <c r="O82" s="230"/>
-      <c r="P82" s="224"/>
-      <c r="Q82" s="204" t="s">
+      <c r="O82" s="296"/>
+      <c r="P82" s="290"/>
+      <c r="Q82" s="270" t="s">
         <v>70</v>
       </c>
-      <c r="R82" s="205"/>
-      <c r="S82" s="210"/>
-      <c r="T82" s="204" t="s">
+      <c r="R82" s="271"/>
+      <c r="S82" s="276"/>
+      <c r="T82" s="270" t="s">
         <v>71</v>
       </c>
-      <c r="U82" s="194"/>
-      <c r="V82" s="194"/>
+      <c r="U82" s="260"/>
+      <c r="V82" s="260"/>
     </row>
     <row r="83" spans="2:35" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B83" s="216"/>
-      <c r="C83" s="217"/>
-      <c r="D83" s="217"/>
-      <c r="E83" s="217"/>
-      <c r="F83" s="217"/>
-      <c r="G83" s="217"/>
-      <c r="H83" s="218"/>
-      <c r="I83" s="198"/>
+      <c r="B83" s="282"/>
+      <c r="C83" s="283"/>
+      <c r="D83" s="283"/>
+      <c r="E83" s="283"/>
+      <c r="F83" s="283"/>
+      <c r="G83" s="283"/>
+      <c r="H83" s="284"/>
+      <c r="I83" s="264"/>
       <c r="J83" s="91"/>
       <c r="K83" s="91"/>
       <c r="L83" s="91"/>
-      <c r="M83" s="225"/>
-      <c r="N83" s="228"/>
-      <c r="O83" s="231"/>
-      <c r="P83" s="225"/>
-      <c r="Q83" s="206"/>
-      <c r="R83" s="207"/>
-      <c r="S83" s="211"/>
-      <c r="T83" s="206"/>
-      <c r="U83" s="194"/>
-      <c r="V83" s="194"/>
+      <c r="M83" s="291"/>
+      <c r="N83" s="294"/>
+      <c r="O83" s="297"/>
+      <c r="P83" s="291"/>
+      <c r="Q83" s="272"/>
+      <c r="R83" s="273"/>
+      <c r="S83" s="277"/>
+      <c r="T83" s="272"/>
+      <c r="U83" s="260"/>
+      <c r="V83" s="260"/>
     </row>
     <row r="84" spans="2:35" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B84" s="219"/>
-      <c r="C84" s="220"/>
-      <c r="D84" s="220"/>
-      <c r="E84" s="220"/>
-      <c r="F84" s="220"/>
-      <c r="G84" s="220"/>
-      <c r="H84" s="221"/>
-      <c r="I84" s="223"/>
+      <c r="B84" s="285"/>
+      <c r="C84" s="286"/>
+      <c r="D84" s="286"/>
+      <c r="E84" s="286"/>
+      <c r="F84" s="286"/>
+      <c r="G84" s="286"/>
+      <c r="H84" s="287"/>
+      <c r="I84" s="289"/>
       <c r="J84" s="149"/>
       <c r="K84" s="149"/>
       <c r="L84" s="149"/>
-      <c r="M84" s="226"/>
-      <c r="N84" s="229"/>
-      <c r="O84" s="232"/>
-      <c r="P84" s="226"/>
-      <c r="Q84" s="208"/>
-      <c r="R84" s="209"/>
-      <c r="S84" s="212"/>
-      <c r="T84" s="208"/>
-      <c r="U84" s="194"/>
-      <c r="V84" s="194"/>
+      <c r="M84" s="292"/>
+      <c r="N84" s="295"/>
+      <c r="O84" s="298"/>
+      <c r="P84" s="292"/>
+      <c r="Q84" s="274"/>
+      <c r="R84" s="275"/>
+      <c r="S84" s="278"/>
+      <c r="T84" s="274"/>
+      <c r="U84" s="260"/>
+      <c r="V84" s="260"/>
     </row>
     <row r="85" spans="2:35" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="V85" s="190"/>
@@ -7337,22 +7337,22 @@
       <c r="V88" s="157"/>
     </row>
     <row r="89" spans="2:35" s="156" customFormat="1" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="B89" s="201"/>
-      <c r="C89" s="202"/>
-      <c r="D89" s="202"/>
-      <c r="E89" s="202"/>
-      <c r="F89" s="202"/>
-      <c r="G89" s="202"/>
-      <c r="H89" s="202"/>
-      <c r="I89" s="203"/>
+      <c r="B89" s="267"/>
+      <c r="C89" s="268"/>
+      <c r="D89" s="268"/>
+      <c r="E89" s="268"/>
+      <c r="F89" s="268"/>
+      <c r="G89" s="268"/>
+      <c r="H89" s="268"/>
+      <c r="I89" s="269"/>
       <c r="J89" s="88"/>
       <c r="K89" s="88"/>
       <c r="L89" s="88"/>
-      <c r="M89" s="201"/>
-      <c r="N89" s="202"/>
-      <c r="O89" s="202"/>
-      <c r="P89" s="202"/>
-      <c r="Q89" s="203"/>
+      <c r="M89" s="267"/>
+      <c r="N89" s="268"/>
+      <c r="O89" s="268"/>
+      <c r="P89" s="268"/>
+      <c r="Q89" s="269"/>
       <c r="R89" s="158"/>
       <c r="S89" s="159"/>
       <c r="T89" s="159"/>
@@ -7361,29 +7361,29 @@
       <c r="W89" s="155"/>
     </row>
     <row r="90" spans="2:35" ht="18" x14ac:dyDescent="0.25">
-      <c r="B90" s="195" t="s">
+      <c r="B90" s="261" t="s">
         <v>76</v>
       </c>
-      <c r="C90" s="196"/>
-      <c r="D90" s="196"/>
-      <c r="E90" s="196"/>
-      <c r="F90" s="196"/>
-      <c r="G90" s="196"/>
-      <c r="H90" s="196"/>
-      <c r="I90" s="197"/>
-      <c r="M90" s="195" t="s">
+      <c r="C90" s="262"/>
+      <c r="D90" s="262"/>
+      <c r="E90" s="262"/>
+      <c r="F90" s="262"/>
+      <c r="G90" s="262"/>
+      <c r="H90" s="262"/>
+      <c r="I90" s="263"/>
+      <c r="M90" s="261" t="s">
         <v>76</v>
       </c>
-      <c r="N90" s="196"/>
-      <c r="O90" s="196"/>
-      <c r="P90" s="196"/>
-      <c r="Q90" s="197"/>
-      <c r="R90" s="198" t="s">
+      <c r="N90" s="262"/>
+      <c r="O90" s="262"/>
+      <c r="P90" s="262"/>
+      <c r="Q90" s="263"/>
+      <c r="R90" s="264" t="s">
         <v>77</v>
       </c>
-      <c r="S90" s="199"/>
-      <c r="T90" s="199"/>
-      <c r="U90" s="200"/>
+      <c r="S90" s="265"/>
+      <c r="T90" s="265"/>
+      <c r="U90" s="266"/>
       <c r="V90" s="192"/>
       <c r="W90" s="153"/>
     </row>
@@ -7424,16 +7424,16 @@
       <c r="V93" s="154"/>
     </row>
     <row r="94" spans="2:35" s="156" customFormat="1" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="B94" s="201" t="s">
+      <c r="B94" s="267" t="s">
         <v>87</v>
       </c>
-      <c r="C94" s="202"/>
-      <c r="D94" s="202"/>
-      <c r="E94" s="202"/>
-      <c r="F94" s="202"/>
-      <c r="G94" s="202"/>
-      <c r="H94" s="202"/>
-      <c r="I94" s="203"/>
+      <c r="C94" s="268"/>
+      <c r="D94" s="268"/>
+      <c r="E94" s="268"/>
+      <c r="F94" s="268"/>
+      <c r="G94" s="268"/>
+      <c r="H94" s="268"/>
+      <c r="I94" s="269"/>
       <c r="J94" s="88"/>
       <c r="K94" s="88"/>
       <c r="L94" s="88"/>
@@ -7452,24 +7452,24 @@
       <c r="W94" s="155"/>
     </row>
     <row r="95" spans="2:35" ht="18" x14ac:dyDescent="0.25">
-      <c r="B95" s="195" t="s">
+      <c r="B95" s="261" t="s">
         <v>80</v>
       </c>
-      <c r="C95" s="196"/>
-      <c r="D95" s="196"/>
-      <c r="E95" s="196"/>
-      <c r="F95" s="196"/>
-      <c r="G95" s="196"/>
-      <c r="H95" s="196"/>
-      <c r="I95" s="197"/>
+      <c r="C95" s="262"/>
+      <c r="D95" s="262"/>
+      <c r="E95" s="262"/>
+      <c r="F95" s="262"/>
+      <c r="G95" s="262"/>
+      <c r="H95" s="262"/>
+      <c r="I95" s="263"/>
       <c r="M95" s="153"/>
       <c r="Q95" s="86"/>
-      <c r="R95" s="198" t="s">
+      <c r="R95" s="264" t="s">
         <v>81</v>
       </c>
-      <c r="S95" s="199"/>
-      <c r="T95" s="199"/>
-      <c r="U95" s="200"/>
+      <c r="S95" s="265"/>
+      <c r="T95" s="265"/>
+      <c r="U95" s="266"/>
       <c r="V95" s="164"/>
     </row>
     <row r="96" spans="2:35" ht="12.75" x14ac:dyDescent="0.25">
@@ -7511,80 +7511,36 @@
     <row r="103" spans="2:23" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="126">
-    <mergeCell ref="U70:V70"/>
-    <mergeCell ref="U71:V71"/>
-    <mergeCell ref="U72:V72"/>
-    <mergeCell ref="U73:V73"/>
-    <mergeCell ref="S76:V76"/>
-    <mergeCell ref="U65:V65"/>
-    <mergeCell ref="U66:V66"/>
-    <mergeCell ref="U67:V67"/>
-    <mergeCell ref="U68:V68"/>
-    <mergeCell ref="U69:V69"/>
-    <mergeCell ref="U60:V60"/>
-    <mergeCell ref="U61:V61"/>
-    <mergeCell ref="U62:V62"/>
-    <mergeCell ref="U63:V63"/>
-    <mergeCell ref="U64:V64"/>
-    <mergeCell ref="U55:V55"/>
-    <mergeCell ref="U56:V56"/>
-    <mergeCell ref="U57:V57"/>
-    <mergeCell ref="U58:V58"/>
-    <mergeCell ref="U59:V59"/>
-    <mergeCell ref="U50:V50"/>
-    <mergeCell ref="U51:V51"/>
-    <mergeCell ref="U52:V52"/>
-    <mergeCell ref="U53:V53"/>
-    <mergeCell ref="U54:V54"/>
-    <mergeCell ref="U45:V45"/>
-    <mergeCell ref="U46:V46"/>
-    <mergeCell ref="U47:V47"/>
-    <mergeCell ref="U48:V48"/>
-    <mergeCell ref="U49:V49"/>
-    <mergeCell ref="U40:V40"/>
-    <mergeCell ref="U41:V41"/>
-    <mergeCell ref="U42:V42"/>
-    <mergeCell ref="U43:V43"/>
-    <mergeCell ref="U44:V44"/>
-    <mergeCell ref="U35:V35"/>
-    <mergeCell ref="U36:V36"/>
-    <mergeCell ref="U37:V37"/>
-    <mergeCell ref="U38:V38"/>
-    <mergeCell ref="U39:V39"/>
-    <mergeCell ref="U30:V30"/>
-    <mergeCell ref="U31:V31"/>
-    <mergeCell ref="U32:V32"/>
-    <mergeCell ref="U33:V33"/>
-    <mergeCell ref="U34:V34"/>
-    <mergeCell ref="U25:V25"/>
-    <mergeCell ref="U26:V26"/>
-    <mergeCell ref="U27:V27"/>
-    <mergeCell ref="U28:V28"/>
-    <mergeCell ref="U29:V29"/>
-    <mergeCell ref="U20:V20"/>
-    <mergeCell ref="U21:V21"/>
-    <mergeCell ref="U22:V22"/>
-    <mergeCell ref="U23:V23"/>
-    <mergeCell ref="U24:V24"/>
-    <mergeCell ref="U15:V15"/>
-    <mergeCell ref="U16:V16"/>
-    <mergeCell ref="U17:V17"/>
-    <mergeCell ref="U18:V18"/>
-    <mergeCell ref="U19:V19"/>
-    <mergeCell ref="U7:V7"/>
-    <mergeCell ref="U8:V8"/>
-    <mergeCell ref="U13:V13"/>
-    <mergeCell ref="U14:V14"/>
-    <mergeCell ref="F2:S2"/>
-    <mergeCell ref="X2:X5"/>
-    <mergeCell ref="F5:M5"/>
-    <mergeCell ref="T5:U5"/>
-    <mergeCell ref="F7:M7"/>
-    <mergeCell ref="X7:X8"/>
-    <mergeCell ref="F8:M8"/>
-    <mergeCell ref="S10:V10"/>
-    <mergeCell ref="S11:V11"/>
-    <mergeCell ref="U2:V3"/>
+    <mergeCell ref="U82:V84"/>
+    <mergeCell ref="B90:I90"/>
+    <mergeCell ref="M90:Q90"/>
+    <mergeCell ref="R90:U90"/>
+    <mergeCell ref="B94:I94"/>
+    <mergeCell ref="B95:I95"/>
+    <mergeCell ref="R95:U95"/>
+    <mergeCell ref="Q82:R84"/>
+    <mergeCell ref="S82:S84"/>
+    <mergeCell ref="T82:T84"/>
+    <mergeCell ref="B89:I89"/>
+    <mergeCell ref="M89:Q89"/>
+    <mergeCell ref="B82:H84"/>
+    <mergeCell ref="I82:I84"/>
+    <mergeCell ref="M82:M84"/>
+    <mergeCell ref="N82:N84"/>
+    <mergeCell ref="O82:P84"/>
+    <mergeCell ref="B74:G74"/>
+    <mergeCell ref="F76:I76"/>
+    <mergeCell ref="M76:N76"/>
+    <mergeCell ref="O76:Q76"/>
+    <mergeCell ref="X78:X80"/>
+    <mergeCell ref="F80:I80"/>
+    <mergeCell ref="M80:N80"/>
+    <mergeCell ref="P80:Q80"/>
+    <mergeCell ref="F78:I78"/>
+    <mergeCell ref="M78:N78"/>
+    <mergeCell ref="P78:Q78"/>
+    <mergeCell ref="S78:V78"/>
+    <mergeCell ref="S80:V80"/>
     <mergeCell ref="B10:B12"/>
     <mergeCell ref="C10:C12"/>
     <mergeCell ref="D10:D12"/>
@@ -7607,36 +7563,80 @@
     <mergeCell ref="AD10:AD12"/>
     <mergeCell ref="AE10:AE12"/>
     <mergeCell ref="U12:V12"/>
-    <mergeCell ref="B74:G74"/>
-    <mergeCell ref="F76:I76"/>
-    <mergeCell ref="M76:N76"/>
-    <mergeCell ref="O76:Q76"/>
-    <mergeCell ref="X78:X80"/>
-    <mergeCell ref="F80:I80"/>
-    <mergeCell ref="M80:N80"/>
-    <mergeCell ref="P80:Q80"/>
-    <mergeCell ref="F78:I78"/>
-    <mergeCell ref="M78:N78"/>
-    <mergeCell ref="P78:Q78"/>
-    <mergeCell ref="S78:V78"/>
-    <mergeCell ref="S80:V80"/>
-    <mergeCell ref="U82:V84"/>
-    <mergeCell ref="B90:I90"/>
-    <mergeCell ref="M90:Q90"/>
-    <mergeCell ref="R90:U90"/>
-    <mergeCell ref="B94:I94"/>
-    <mergeCell ref="B95:I95"/>
-    <mergeCell ref="R95:U95"/>
-    <mergeCell ref="Q82:R84"/>
-    <mergeCell ref="S82:S84"/>
-    <mergeCell ref="T82:T84"/>
-    <mergeCell ref="B89:I89"/>
-    <mergeCell ref="M89:Q89"/>
-    <mergeCell ref="B82:H84"/>
-    <mergeCell ref="I82:I84"/>
-    <mergeCell ref="M82:M84"/>
-    <mergeCell ref="N82:N84"/>
-    <mergeCell ref="O82:P84"/>
+    <mergeCell ref="U7:V7"/>
+    <mergeCell ref="U8:V8"/>
+    <mergeCell ref="U13:V13"/>
+    <mergeCell ref="U14:V14"/>
+    <mergeCell ref="F2:S2"/>
+    <mergeCell ref="X2:X5"/>
+    <mergeCell ref="F5:M5"/>
+    <mergeCell ref="T5:U5"/>
+    <mergeCell ref="F7:M7"/>
+    <mergeCell ref="X7:X8"/>
+    <mergeCell ref="F8:M8"/>
+    <mergeCell ref="S10:V10"/>
+    <mergeCell ref="S11:V11"/>
+    <mergeCell ref="U2:V3"/>
+    <mergeCell ref="U20:V20"/>
+    <mergeCell ref="U21:V21"/>
+    <mergeCell ref="U22:V22"/>
+    <mergeCell ref="U23:V23"/>
+    <mergeCell ref="U24:V24"/>
+    <mergeCell ref="U15:V15"/>
+    <mergeCell ref="U16:V16"/>
+    <mergeCell ref="U17:V17"/>
+    <mergeCell ref="U18:V18"/>
+    <mergeCell ref="U19:V19"/>
+    <mergeCell ref="U30:V30"/>
+    <mergeCell ref="U31:V31"/>
+    <mergeCell ref="U32:V32"/>
+    <mergeCell ref="U33:V33"/>
+    <mergeCell ref="U34:V34"/>
+    <mergeCell ref="U25:V25"/>
+    <mergeCell ref="U26:V26"/>
+    <mergeCell ref="U27:V27"/>
+    <mergeCell ref="U28:V28"/>
+    <mergeCell ref="U29:V29"/>
+    <mergeCell ref="U40:V40"/>
+    <mergeCell ref="U41:V41"/>
+    <mergeCell ref="U42:V42"/>
+    <mergeCell ref="U43:V43"/>
+    <mergeCell ref="U44:V44"/>
+    <mergeCell ref="U35:V35"/>
+    <mergeCell ref="U36:V36"/>
+    <mergeCell ref="U37:V37"/>
+    <mergeCell ref="U38:V38"/>
+    <mergeCell ref="U39:V39"/>
+    <mergeCell ref="U50:V50"/>
+    <mergeCell ref="U51:V51"/>
+    <mergeCell ref="U52:V52"/>
+    <mergeCell ref="U53:V53"/>
+    <mergeCell ref="U54:V54"/>
+    <mergeCell ref="U45:V45"/>
+    <mergeCell ref="U46:V46"/>
+    <mergeCell ref="U47:V47"/>
+    <mergeCell ref="U48:V48"/>
+    <mergeCell ref="U49:V49"/>
+    <mergeCell ref="U60:V60"/>
+    <mergeCell ref="U61:V61"/>
+    <mergeCell ref="U62:V62"/>
+    <mergeCell ref="U63:V63"/>
+    <mergeCell ref="U64:V64"/>
+    <mergeCell ref="U55:V55"/>
+    <mergeCell ref="U56:V56"/>
+    <mergeCell ref="U57:V57"/>
+    <mergeCell ref="U58:V58"/>
+    <mergeCell ref="U59:V59"/>
+    <mergeCell ref="U70:V70"/>
+    <mergeCell ref="U71:V71"/>
+    <mergeCell ref="U72:V72"/>
+    <mergeCell ref="U73:V73"/>
+    <mergeCell ref="S76:V76"/>
+    <mergeCell ref="U65:V65"/>
+    <mergeCell ref="U66:V66"/>
+    <mergeCell ref="U67:V67"/>
+    <mergeCell ref="U68:V68"/>
+    <mergeCell ref="U69:V69"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.19685039370078741" right="0" top="0" bottom="0" header="0" footer="0.19685039370078741"/>
